--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -1791,15 +1791,15 @@
         <v/>
       </c>
       <c r="I18" s="17">
-        <f>IF($H18="","",IFERROR(VLOOKUP($H18,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H18="","",IFERROR(VLOOKUP($H18,PQ_Diario!$A:$D,2,0),V18))</f>
         <v/>
       </c>
       <c r="J18" s="17">
-        <f>IF($H18="","",IFERROR(VLOOKUP($H18,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H18="","",IFERROR(VLOOKUP($H18,PQ_Diario!$A:$D,3,0),W18))</f>
         <v/>
       </c>
       <c r="K18" s="17">
-        <f>IF($H18="","",IFERROR(VLOOKUP($H18,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H18="","",IFERROR(VLOOKUP($H18,PQ_Diario!$A:$D,4,0),X18))</f>
         <v/>
       </c>
       <c r="Q18" s="21">
@@ -1818,6 +1818,15 @@
       </c>
       <c r="U18" s="19" t="n">
         <v>0.06423</v>
+      </c>
+      <c r="V18" s="20" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="W18" s="20" t="n">
+        <v>121.39</v>
+      </c>
+      <c r="X18" s="20" t="n">
+        <v>237.53</v>
       </c>
     </row>
     <row r="19">
@@ -5984,7 +5993,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6039,7 +6048,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>139.75</v>
+        <v>138.4</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>0</v>
@@ -6070,7 +6079,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>153.59</v>
+        <v>152</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>0</v>
@@ -6101,7 +6110,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>155.6</v>
+        <v>151.75</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6132,7 +6141,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>157.55</v>
+        <v>157</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6163,7 +6172,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>137.96</v>
+        <v>137.41</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6194,7 +6203,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>90.27</v>
+        <v>89.72</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6220,7 +6229,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>149.6</v>
+        <v>147.33</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6246,7 +6255,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>128.3</v>
+        <v>127.75</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6272,7 +6281,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>61.65</v>
+        <v>60.8</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6298,7 +6307,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>87.31</v>
+        <v>88</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>3</v>
@@ -6324,7 +6333,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>95.18000000000001</v>
+        <v>94.88</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6350,7 +6359,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>76.93000000000001</v>
+        <v>76.88</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6376,7 +6385,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>49.35</v>
+        <v>49.3</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6402,7 +6411,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>93</v>
+        <v>92.75</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6428,7 +6437,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>65.3</v>
+        <v>65.25</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6454,7 +6463,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>57.7</v>
+        <v>57.8</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -1858,15 +1858,15 @@
         <v/>
       </c>
       <c r="I19" s="17">
-        <f>IF($H19="","",IFERROR(VLOOKUP($H19,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H19="","",IFERROR(VLOOKUP($H19,PQ_Diario!$A:$D,2,0),V19))</f>
         <v/>
       </c>
       <c r="J19" s="17">
-        <f>IF($H19="","",IFERROR(VLOOKUP($H19,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H19="","",IFERROR(VLOOKUP($H19,PQ_Diario!$A:$D,3,0),W19))</f>
         <v/>
       </c>
       <c r="K19" s="17">
-        <f>IF($H19="","",IFERROR(VLOOKUP($H19,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H19="","",IFERROR(VLOOKUP($H19,PQ_Diario!$A:$D,4,0),X19))</f>
         <v/>
       </c>
       <c r="S19" s="19" t="n">
@@ -1877,6 +1877,15 @@
       </c>
       <c r="U19" s="19" t="n">
         <v>0.03621</v>
+      </c>
+      <c r="V19" s="20" t="n">
+        <v>40.53</v>
+      </c>
+      <c r="W19" s="20" t="n">
+        <v>177.44</v>
+      </c>
+      <c r="X19" s="20" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="20">
@@ -5993,7 +6002,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -1917,15 +1917,15 @@
         <v/>
       </c>
       <c r="I20" s="17">
-        <f>IF($H20="","",IFERROR(VLOOKUP($H20,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H20="","",IFERROR(VLOOKUP($H20,PQ_Diario!$A:$D,2,0),V20))</f>
         <v/>
       </c>
       <c r="J20" s="17">
-        <f>IF($H20="","",IFERROR(VLOOKUP($H20,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H20="","",IFERROR(VLOOKUP($H20,PQ_Diario!$A:$D,3,0),W20))</f>
         <v/>
       </c>
       <c r="K20" s="17">
-        <f>IF($H20="","",IFERROR(VLOOKUP($H20,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H20="","",IFERROR(VLOOKUP($H20,PQ_Diario!$A:$D,4,0),X20))</f>
         <v/>
       </c>
       <c r="S20" s="19" t="n">
@@ -1936,6 +1936,15 @@
       </c>
       <c r="U20" s="19" t="n">
         <v>0.01494</v>
+      </c>
+      <c r="V20" s="20" t="n">
+        <v>35.67</v>
+      </c>
+      <c r="W20" s="20" t="n">
+        <v>167.33</v>
+      </c>
+      <c r="X20" s="20" t="n">
+        <v>268.06</v>
       </c>
     </row>
     <row r="21">
@@ -6002,7 +6011,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -1976,15 +1976,15 @@
         <v/>
       </c>
       <c r="I21" s="17">
-        <f>IF($H21="","",IFERROR(VLOOKUP($H21,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H21="","",IFERROR(VLOOKUP($H21,PQ_Diario!$A:$D,2,0),V21))</f>
         <v/>
       </c>
       <c r="J21" s="17">
-        <f>IF($H21="","",IFERROR(VLOOKUP($H21,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H21="","",IFERROR(VLOOKUP($H21,PQ_Diario!$A:$D,3,0),W21))</f>
         <v/>
       </c>
       <c r="K21" s="17">
-        <f>IF($H21="","",IFERROR(VLOOKUP($H21,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H21="","",IFERROR(VLOOKUP($H21,PQ_Diario!$A:$D,4,0),X21))</f>
         <v/>
       </c>
       <c r="S21" s="19" t="n">
@@ -1995,6 +1995,15 @@
       </c>
       <c r="U21" s="19" t="n">
         <v>0.01337</v>
+      </c>
+      <c r="V21" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" s="20" t="n">
+        <v>104.63</v>
+      </c>
+      <c r="X21" s="20" t="n">
+        <v>196.18</v>
       </c>
     </row>
     <row r="22">
@@ -6011,7 +6020,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6066,7 +6075,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>138.4</v>
+        <v>145</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>0</v>
@@ -6097,7 +6106,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>0</v>
@@ -6128,7 +6137,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>151.75</v>
+        <v>159.6</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6159,7 +6168,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>157</v>
+        <v>168.68</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6190,7 +6199,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>137.41</v>
+        <v>147.63</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6221,7 +6230,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>89.72</v>
+        <v>96.39</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6247,7 +6256,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>147.33</v>
+        <v>155.46</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6273,7 +6282,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>127.75</v>
+        <v>137.25</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6299,7 +6308,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>60.8</v>
+        <v>64</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6325,7 +6334,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>88</v>
+        <v>88.25</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>3</v>
@@ -6351,7 +6360,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>94.88</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6377,7 +6386,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>76.88</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6403,7 +6412,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>49.3</v>
+        <v>50.81</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6429,7 +6438,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>92.75</v>
+        <v>96.89</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6455,7 +6464,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>65.25</v>
+        <v>67.25</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6481,7 +6490,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>57.8</v>
+        <v>58.65</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -2035,15 +2035,15 @@
         <v/>
       </c>
       <c r="I22" s="17">
-        <f>IF($H22="","",IFERROR(VLOOKUP($H22,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H22="","",IFERROR(VLOOKUP($H22,PQ_Diario!$A:$D,2,0),V22))</f>
         <v/>
       </c>
       <c r="J22" s="17">
-        <f>IF($H22="","",IFERROR(VLOOKUP($H22,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H22="","",IFERROR(VLOOKUP($H22,PQ_Diario!$A:$D,3,0),W22))</f>
         <v/>
       </c>
       <c r="K22" s="17">
-        <f>IF($H22="","",IFERROR(VLOOKUP($H22,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H22="","",IFERROR(VLOOKUP($H22,PQ_Diario!$A:$D,4,0),X22))</f>
         <v/>
       </c>
       <c r="S22" s="19" t="n">
@@ -2054,6 +2054,15 @@
       </c>
       <c r="U22" s="19" t="n">
         <v>0.03306</v>
+      </c>
+      <c r="V22" s="20" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="W22" s="20" t="n">
+        <v>127.41</v>
+      </c>
+      <c r="X22" s="20" t="n">
+        <v>244.11</v>
       </c>
     </row>
     <row r="23">
@@ -6020,7 +6029,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6075,7 +6084,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>145</v>
+        <v>138.75</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>0</v>
@@ -6106,7 +6115,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>0</v>
@@ -6137,7 +6146,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>159.6</v>
+        <v>154.01</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6168,7 +6177,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>168.68</v>
+        <v>161</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6199,7 +6208,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>147.63</v>
+        <v>141.28</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6230,7 +6239,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>96.39</v>
+        <v>92.23999999999999</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6256,7 +6265,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>155.46</v>
+        <v>149.51</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6282,7 +6291,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>137.25</v>
+        <v>131.2</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6308,7 +6317,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6334,7 +6343,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>88.25</v>
+        <v>81.25</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>3</v>
@@ -6360,7 +6369,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>98.59999999999999</v>
+        <v>92.11</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6386,7 +6395,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>79.23999999999999</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6412,7 +6421,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>50.81</v>
+        <v>48.06</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6438,7 +6447,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>96.89</v>
+        <v>91</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6464,7 +6473,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>67.25</v>
+        <v>64.5</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6490,7 +6499,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>58.65</v>
+        <v>57.5</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -2094,15 +2094,15 @@
         <v/>
       </c>
       <c r="I23" s="17">
-        <f>IF($H23="","",IFERROR(VLOOKUP($H23,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H23="","",IFERROR(VLOOKUP($H23,PQ_Diario!$A:$D,2,0),V23))</f>
         <v/>
       </c>
       <c r="J23" s="17">
-        <f>IF($H23="","",IFERROR(VLOOKUP($H23,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H23="","",IFERROR(VLOOKUP($H23,PQ_Diario!$A:$D,3,0),W23))</f>
         <v/>
       </c>
       <c r="K23" s="17">
-        <f>IF($H23="","",IFERROR(VLOOKUP($H23,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H23="","",IFERROR(VLOOKUP($H23,PQ_Diario!$A:$D,4,0),X23))</f>
         <v/>
       </c>
       <c r="S23" s="19" t="n">
@@ -2113,6 +2113,15 @@
       </c>
       <c r="U23" s="19" t="n">
         <v>0.05189</v>
+      </c>
+      <c r="V23" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" s="20" t="n">
+        <v>124.78</v>
+      </c>
+      <c r="X23" s="20" t="n">
+        <v>228.78</v>
       </c>
     </row>
     <row r="24">
@@ -6029,7 +6038,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6084,7 +6093,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>138.75</v>
+        <v>136.25</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>0</v>
@@ -6115,7 +6124,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>156</v>
+        <v>151.81</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>0</v>
@@ -6146,7 +6155,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>154.01</v>
+        <v>147.17</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6177,7 +6186,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6208,7 +6217,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>141.28</v>
+        <v>132.22</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6239,7 +6248,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>92.23999999999999</v>
+        <v>86.33</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6265,7 +6274,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>149.51</v>
+        <v>145</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6291,7 +6300,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>131.2</v>
+        <v>126</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6317,7 +6326,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>60</v>
+        <v>56.9</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6343,7 +6352,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>81.25</v>
+        <v>82.23</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>3</v>
@@ -6369,7 +6378,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>92.11</v>
+        <v>88.95999999999999</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6395,7 +6404,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>76.48999999999999</v>
+        <v>73.23999999999999</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6421,7 +6430,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>48.06</v>
+        <v>45.82</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6447,7 +6456,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>91</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6473,7 +6482,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>64.5</v>
+        <v>61</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -2153,15 +2153,15 @@
         <v/>
       </c>
       <c r="I24" s="17">
-        <f>IF($H24="","",IFERROR(VLOOKUP($H24,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H24="","",IFERROR(VLOOKUP($H24,PQ_Diario!$A:$D,2,0),V24))</f>
         <v/>
       </c>
       <c r="J24" s="17">
-        <f>IF($H24="","",IFERROR(VLOOKUP($H24,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H24="","",IFERROR(VLOOKUP($H24,PQ_Diario!$A:$D,3,0),W24))</f>
         <v/>
       </c>
       <c r="K24" s="17">
-        <f>IF($H24="","",IFERROR(VLOOKUP($H24,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H24="","",IFERROR(VLOOKUP($H24,PQ_Diario!$A:$D,4,0),X24))</f>
         <v/>
       </c>
       <c r="S24" s="19" t="n">
@@ -2172,6 +2172,15 @@
       </c>
       <c r="U24" s="19" t="n">
         <v>0.07045</v>
+      </c>
+      <c r="V24" s="20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W24" s="20" t="n">
+        <v>110.26</v>
+      </c>
+      <c r="X24" s="20" t="n">
+        <v>201.15</v>
       </c>
     </row>
     <row r="25">
@@ -6038,7 +6047,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6093,7 +6102,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>136.25</v>
+        <v>135.1</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>0</v>
@@ -6124,7 +6133,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>151.81</v>
+        <v>149.6</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>0</v>
@@ -6155,7 +6164,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>147.17</v>
+        <v>144.08</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6186,7 +6195,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6217,7 +6226,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>132.22</v>
+        <v>134.44</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6248,7 +6257,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>86.33</v>
+        <v>87.42</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6274,7 +6283,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>145</v>
+        <v>142.85</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6300,7 +6309,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6326,7 +6335,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>56.9</v>
+        <v>55</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6352,7 +6361,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>82.23</v>
+        <v>81</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>3</v>
@@ -6378,7 +6387,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>88.95999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6404,7 +6413,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>73.23999999999999</v>
+        <v>72.34</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6430,7 +6439,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>45.82</v>
+        <v>45.45</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6456,7 +6465,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>88.40000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6508,7 +6517,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>57.5</v>
+        <v>57.25</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -2212,15 +2212,15 @@
         <v/>
       </c>
       <c r="I25" s="17">
-        <f>IF($H25="","",IFERROR(VLOOKUP($H25,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H25="","",IFERROR(VLOOKUP($H25,PQ_Diario!$A:$D,2,0),V25))</f>
         <v/>
       </c>
       <c r="J25" s="17">
-        <f>IF($H25="","",IFERROR(VLOOKUP($H25,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H25="","",IFERROR(VLOOKUP($H25,PQ_Diario!$A:$D,3,0),W25))</f>
         <v/>
       </c>
       <c r="K25" s="17">
-        <f>IF($H25="","",IFERROR(VLOOKUP($H25,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H25="","",IFERROR(VLOOKUP($H25,PQ_Diario!$A:$D,4,0),X25))</f>
         <v/>
       </c>
       <c r="S25" s="19" t="n">
@@ -2231,6 +2231,15 @@
       </c>
       <c r="U25" s="19" t="n">
         <v>0.08558</v>
+      </c>
+      <c r="V25" s="20" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="W25" s="20" t="n">
+        <v>112.56</v>
+      </c>
+      <c r="X25" s="20" t="n">
+        <v>225.57</v>
       </c>
     </row>
     <row r="26">
@@ -6047,7 +6056,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6102,7 +6111,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>135.1</v>
+        <v>139</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>0</v>
@@ -6133,7 +6142,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>149.6</v>
+        <v>154.34</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>0</v>
@@ -6164,7 +6173,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>144.08</v>
+        <v>147.31</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6195,7 +6204,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>154</v>
+        <v>155.37</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6226,7 +6235,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>134.44</v>
+        <v>135.63</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6257,7 +6266,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>87.42</v>
+        <v>89.91</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6283,7 +6292,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>142.85</v>
+        <v>146.8</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6309,7 +6318,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>125</v>
+        <v>126.7</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6335,7 +6344,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>55</v>
+        <v>56.85</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6361,7 +6370,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>81</v>
+        <v>83.5</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>3</v>
@@ -6387,7 +6396,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>86.7</v>
+        <v>91.42</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6413,7 +6422,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>72.34</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6439,7 +6448,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>45.45</v>
+        <v>45.65</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6465,7 +6474,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>86.8</v>
+        <v>89.5</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6491,7 +6500,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>61</v>
+        <v>61.2</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6517,7 +6526,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>57.25</v>
+        <v>58</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -6056,7 +6056,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -2271,15 +2271,15 @@
         <v/>
       </c>
       <c r="I26" s="17">
-        <f>IF($H26="","",IFERROR(VLOOKUP($H26,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H26="","",IFERROR(VLOOKUP($H26,PQ_Diario!$A:$D,2,0),V26))</f>
         <v/>
       </c>
       <c r="J26" s="17">
-        <f>IF($H26="","",IFERROR(VLOOKUP($H26,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H26="","",IFERROR(VLOOKUP($H26,PQ_Diario!$A:$D,3,0),W26))</f>
         <v/>
       </c>
       <c r="K26" s="17">
-        <f>IF($H26="","",IFERROR(VLOOKUP($H26,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H26="","",IFERROR(VLOOKUP($H26,PQ_Diario!$A:$D,4,0),X26))</f>
         <v/>
       </c>
       <c r="S26" s="19" t="n">
@@ -2290,6 +2290,15 @@
       </c>
       <c r="U26" s="19" t="n">
         <v>0.0725</v>
+      </c>
+      <c r="V26" s="20" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W26" s="20" t="n">
+        <v>138.77</v>
+      </c>
+      <c r="X26" s="20" t="n">
+        <v>276.54</v>
       </c>
     </row>
     <row r="27">
@@ -2321,15 +2330,15 @@
         <v/>
       </c>
       <c r="I27" s="17">
-        <f>IF($H27="","",IFERROR(VLOOKUP($H27,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H27="","",IFERROR(VLOOKUP($H27,PQ_Diario!$A:$D,2,0),V27))</f>
         <v/>
       </c>
       <c r="J27" s="17">
-        <f>IF($H27="","",IFERROR(VLOOKUP($H27,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H27="","",IFERROR(VLOOKUP($H27,PQ_Diario!$A:$D,3,0),W27))</f>
         <v/>
       </c>
       <c r="K27" s="17">
-        <f>IF($H27="","",IFERROR(VLOOKUP($H27,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H27="","",IFERROR(VLOOKUP($H27,PQ_Diario!$A:$D,4,0),X27))</f>
         <v/>
       </c>
       <c r="S27" s="19" t="n">
@@ -2340,6 +2349,15 @@
       </c>
       <c r="U27" s="19" t="n">
         <v>0.0595</v>
+      </c>
+      <c r="V27" s="20" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="W27" s="20" t="n">
+        <v>156.02</v>
+      </c>
+      <c r="X27" s="20" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="28">
@@ -6056,7 +6074,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -2389,15 +2389,15 @@
         <v/>
       </c>
       <c r="I28" s="17">
-        <f>IF($H28="","",IFERROR(VLOOKUP($H28,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H28="","",IFERROR(VLOOKUP($H28,PQ_Diario!$A:$D,2,0),V28))</f>
         <v/>
       </c>
       <c r="J28" s="17">
-        <f>IF($H28="","",IFERROR(VLOOKUP($H28,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H28="","",IFERROR(VLOOKUP($H28,PQ_Diario!$A:$D,3,0),W28))</f>
         <v/>
       </c>
       <c r="K28" s="17">
-        <f>IF($H28="","",IFERROR(VLOOKUP($H28,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H28="","",IFERROR(VLOOKUP($H28,PQ_Diario!$A:$D,4,0),X28))</f>
         <v/>
       </c>
       <c r="S28" s="19" t="n">
@@ -2408,6 +2408,15 @@
       </c>
       <c r="U28" s="19" t="n">
         <v>0.09408999999999999</v>
+      </c>
+      <c r="V28" s="20" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="W28" s="20" t="n">
+        <v>158.88</v>
+      </c>
+      <c r="X28" s="20" t="n">
+        <v>274.36</v>
       </c>
     </row>
     <row r="29">
@@ -6074,7 +6083,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6129,7 +6138,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>139</v>
+        <v>131.75</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>0</v>
@@ -6160,7 +6169,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>154.34</v>
+        <v>146.13</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>0</v>
@@ -6191,7 +6200,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>147.31</v>
+        <v>138.62</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6222,7 +6231,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>155.37</v>
+        <v>147.67</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6253,7 +6262,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>135.63</v>
+        <v>127.93</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6284,7 +6293,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>89.91</v>
+        <v>82.20999999999999</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6310,7 +6319,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>146.8</v>
+        <v>138.75</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6336,7 +6345,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>126.7</v>
+        <v>119</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6362,7 +6371,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>56.85</v>
+        <v>55.5</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6388,7 +6397,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>83.5</v>
+        <v>82.25</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>3</v>
@@ -6414,7 +6423,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>91.42</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6440,7 +6449,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>72.54000000000001</v>
+        <v>70.64</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6466,7 +6475,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>45.65</v>
+        <v>43.75</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6492,7 +6501,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>89.5</v>
+        <v>86</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6518,7 +6527,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>61.2</v>
+        <v>59.3</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6544,7 +6553,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>58</v>
+        <v>57.4</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -2448,15 +2448,15 @@
         <v/>
       </c>
       <c r="I29" s="17">
-        <f>IF($H29="","",IFERROR(VLOOKUP($H29,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H29="","",IFERROR(VLOOKUP($H29,PQ_Diario!$A:$D,2,0),V29))</f>
         <v/>
       </c>
       <c r="J29" s="17">
-        <f>IF($H29="","",IFERROR(VLOOKUP($H29,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H29="","",IFERROR(VLOOKUP($H29,PQ_Diario!$A:$D,3,0),W29))</f>
         <v/>
       </c>
       <c r="K29" s="17">
-        <f>IF($H29="","",IFERROR(VLOOKUP($H29,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H29="","",IFERROR(VLOOKUP($H29,PQ_Diario!$A:$D,4,0),X29))</f>
         <v/>
       </c>
       <c r="S29" s="19" t="n">
@@ -2467,6 +2467,15 @@
       </c>
       <c r="U29" s="19" t="n">
         <v>0.10005</v>
+      </c>
+      <c r="V29" s="20" t="n">
+        <v>17.62</v>
+      </c>
+      <c r="W29" s="20" t="n">
+        <v>157.24</v>
+      </c>
+      <c r="X29" s="20" t="n">
+        <v>288.23</v>
       </c>
     </row>
     <row r="30">
@@ -6083,7 +6092,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6138,7 +6147,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>131.75</v>
+        <v>131.4</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>0</v>
@@ -6169,7 +6178,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>146.13</v>
+        <v>145.6</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>0</v>
@@ -6200,7 +6209,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>138.62</v>
+        <v>137.25</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6231,7 +6240,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>147.67</v>
+        <v>147</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6262,7 +6271,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>127.93</v>
+        <v>123.75</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6293,7 +6302,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>82.20999999999999</v>
+        <v>78.53</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6319,7 +6328,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>138.75</v>
+        <v>138</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6345,7 +6354,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>119</v>
+        <v>116.2</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6371,7 +6380,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>55.5</v>
+        <v>54.5</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6397,7 +6406,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>82.25</v>
+        <v>81.84</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>3</v>
@@ -6423,7 +6432,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>87.65000000000001</v>
+        <v>87.81999999999999</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6449,7 +6458,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>70.64</v>
+        <v>69.34</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6475,7 +6484,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>43.75</v>
+        <v>42.45</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6501,7 +6510,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6527,7 +6536,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>59.3</v>
+        <v>58</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6553,7 +6562,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>57.4</v>
+        <v>57.25</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -2507,15 +2507,15 @@
         <v/>
       </c>
       <c r="I30" s="17">
-        <f>IF($H30="","",IFERROR(VLOOKUP($H30,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H30="","",IFERROR(VLOOKUP($H30,PQ_Diario!$A:$D,2,0),V30))</f>
         <v/>
       </c>
       <c r="J30" s="17">
-        <f>IF($H30="","",IFERROR(VLOOKUP($H30,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H30="","",IFERROR(VLOOKUP($H30,PQ_Diario!$A:$D,3,0),W30))</f>
         <v/>
       </c>
       <c r="K30" s="17">
-        <f>IF($H30="","",IFERROR(VLOOKUP($H30,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H30="","",IFERROR(VLOOKUP($H30,PQ_Diario!$A:$D,4,0),X30))</f>
         <v/>
       </c>
       <c r="S30" s="19" t="n">
@@ -2526,6 +2526,15 @@
       </c>
       <c r="U30" s="19" t="n">
         <v>0.08304</v>
+      </c>
+      <c r="V30" s="20" t="n">
+        <v>19.17</v>
+      </c>
+      <c r="W30" s="20" t="n">
+        <v>158.92</v>
+      </c>
+      <c r="X30" s="20" t="n">
+        <v>287.13</v>
       </c>
     </row>
     <row r="31">
@@ -6092,7 +6101,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6147,7 +6156,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>131.4</v>
+        <v>129.35</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>0</v>
@@ -6178,7 +6187,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>145.6</v>
+        <v>143.58</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>0</v>
@@ -6209,7 +6218,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>137.25</v>
+        <v>137.7</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6271,7 +6280,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>123.75</v>
+        <v>122.59</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6302,7 +6311,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>78.53</v>
+        <v>77.54000000000001</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6328,7 +6337,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>138</v>
+        <v>136.8</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6354,7 +6363,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>116.2</v>
+        <v>115.5</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6380,7 +6389,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>54.5</v>
+        <v>55</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6406,7 +6415,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>81.84</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>3</v>
@@ -6432,7 +6441,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>87.81999999999999</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6484,7 +6493,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>42.45</v>
+        <v>42.85</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6510,7 +6519,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>85</v>
+        <v>85.8</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6536,7 +6545,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>58</v>
+        <v>58.4</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -2566,15 +2566,15 @@
         <v/>
       </c>
       <c r="I31" s="17">
-        <f>IF($H31="","",IFERROR(VLOOKUP($H31,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H31="","",IFERROR(VLOOKUP($H31,PQ_Diario!$A:$D,2,0),V31))</f>
         <v/>
       </c>
       <c r="J31" s="17">
-        <f>IF($H31="","",IFERROR(VLOOKUP($H31,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H31="","",IFERROR(VLOOKUP($H31,PQ_Diario!$A:$D,3,0),W31))</f>
         <v/>
       </c>
       <c r="K31" s="17">
-        <f>IF($H31="","",IFERROR(VLOOKUP($H31,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H31="","",IFERROR(VLOOKUP($H31,PQ_Diario!$A:$D,4,0),X31))</f>
         <v/>
       </c>
       <c r="S31" s="19" t="n">
@@ -2585,6 +2585,15 @@
       </c>
       <c r="U31" s="19" t="n">
         <v>0.10093</v>
+      </c>
+      <c r="V31" s="20" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="W31" s="20" t="n">
+        <v>130.62</v>
+      </c>
+      <c r="X31" s="20" t="n">
+        <v>251.08</v>
       </c>
     </row>
     <row r="32">
@@ -6101,7 +6110,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6156,7 +6165,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>129.35</v>
+        <v>133.2</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>0</v>
@@ -6187,7 +6196,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>143.58</v>
+        <v>147.83</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>0</v>
@@ -6218,7 +6227,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>137.7</v>
+        <v>143.24</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6249,7 +6258,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>147</v>
+        <v>147.5</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6280,7 +6289,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>122.59</v>
+        <v>125.57</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6311,7 +6320,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>77.54000000000001</v>
+        <v>80.16</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6337,7 +6346,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>136.8</v>
+        <v>141.35</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6363,7 +6372,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>115.5</v>
+        <v>117.5</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6389,7 +6398,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>55</v>
+        <v>57.49</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6415,7 +6424,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>82.18000000000001</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>3</v>
@@ -6441,7 +6450,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>90.84999999999999</v>
+        <v>92.69</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6467,7 +6476,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>69.34</v>
+        <v>71.94</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6493,7 +6502,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>42.85</v>
+        <v>45.45</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6519,7 +6528,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>85.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6545,7 +6554,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>58.4</v>
+        <v>61</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6571,7 +6580,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>57.25</v>
+        <v>58.75</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -2625,15 +2625,15 @@
         <v/>
       </c>
       <c r="I32" s="17">
-        <f>IF($H32="","",IFERROR(VLOOKUP($H32,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H32="","",IFERROR(VLOOKUP($H32,PQ_Diario!$A:$D,2,0),V32))</f>
         <v/>
       </c>
       <c r="J32" s="17">
-        <f>IF($H32="","",IFERROR(VLOOKUP($H32,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H32="","",IFERROR(VLOOKUP($H32,PQ_Diario!$A:$D,3,0),W32))</f>
         <v/>
       </c>
       <c r="K32" s="17">
-        <f>IF($H32="","",IFERROR(VLOOKUP($H32,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H32="","",IFERROR(VLOOKUP($H32,PQ_Diario!$A:$D,4,0),X32))</f>
         <v/>
       </c>
       <c r="S32" s="19" t="n">
@@ -2644,6 +2644,15 @@
       </c>
       <c r="U32" s="19" t="n">
         <v>0.04494</v>
+      </c>
+      <c r="V32" s="20" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="W32" s="20" t="n">
+        <v>113.65</v>
+      </c>
+      <c r="X32" s="20" t="n">
+        <v>210.26</v>
       </c>
     </row>
     <row r="33">
@@ -6110,7 +6119,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6165,7 +6174,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>133.2</v>
+        <v>128.2</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>0</v>
@@ -6196,7 +6205,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>147.83</v>
+        <v>142.6</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>0</v>
@@ -6227,7 +6236,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>143.24</v>
+        <v>141.2</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6258,7 +6267,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>147.5</v>
+        <v>143</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6289,7 +6298,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>125.57</v>
+        <v>125.2</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6320,7 +6329,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>80.16</v>
+        <v>79.19</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6346,7 +6355,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>141.35</v>
+        <v>137.27</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6372,7 +6381,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>117.5</v>
+        <v>115.5</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6398,7 +6407,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>57.49</v>
+        <v>58.5</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6424,7 +6433,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>84.23999999999999</v>
+        <v>84.5</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>3</v>
@@ -6450,7 +6459,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>92.69</v>
+        <v>92.8</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6476,7 +6485,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>71.94</v>
+        <v>71.44</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6502,7 +6511,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>45.45</v>
+        <v>44.95</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6528,7 +6537,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>87.90000000000001</v>
+        <v>87.75</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6554,7 +6563,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>61</v>
+        <v>60.5</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6580,7 +6589,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>58.75</v>
+        <v>58</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -2684,15 +2684,15 @@
         <v/>
       </c>
       <c r="I33" s="17">
-        <f>IF($H33="","",IFERROR(VLOOKUP($H33,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H33="","",IFERROR(VLOOKUP($H33,PQ_Diario!$A:$D,2,0),V33))</f>
         <v/>
       </c>
       <c r="J33" s="17">
-        <f>IF($H33="","",IFERROR(VLOOKUP($H33,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H33="","",IFERROR(VLOOKUP($H33,PQ_Diario!$A:$D,3,0),W33))</f>
         <v/>
       </c>
       <c r="K33" s="17">
-        <f>IF($H33="","",IFERROR(VLOOKUP($H33,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H33="","",IFERROR(VLOOKUP($H33,PQ_Diario!$A:$D,4,0),X33))</f>
         <v/>
       </c>
       <c r="S33" s="19" t="n">
@@ -2703,6 +2703,15 @@
       </c>
       <c r="U33" s="19" t="n">
         <v>0.02598</v>
+      </c>
+      <c r="V33" s="20" t="n">
+        <v>147.32</v>
+      </c>
+      <c r="W33" s="20" t="n">
+        <v>198.05</v>
+      </c>
+      <c r="X33" s="20" t="n">
+        <v>280.59</v>
       </c>
     </row>
     <row r="34">
@@ -6119,7 +6128,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -2743,15 +2743,15 @@
         <v/>
       </c>
       <c r="I34" s="17">
-        <f>IF($H34="","",IFERROR(VLOOKUP($H34,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H34="","",IFERROR(VLOOKUP($H34,PQ_Diario!$A:$D,2,0),V34))</f>
         <v/>
       </c>
       <c r="J34" s="17">
-        <f>IF($H34="","",IFERROR(VLOOKUP($H34,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H34="","",IFERROR(VLOOKUP($H34,PQ_Diario!$A:$D,3,0),W34))</f>
         <v/>
       </c>
       <c r="K34" s="17">
-        <f>IF($H34="","",IFERROR(VLOOKUP($H34,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H34="","",IFERROR(VLOOKUP($H34,PQ_Diario!$A:$D,4,0),X34))</f>
         <v/>
       </c>
       <c r="S34" s="19" t="n">
@@ -2762,6 +2762,15 @@
       </c>
       <c r="U34" s="19" t="n">
         <v>0.01711</v>
+      </c>
+      <c r="V34" s="20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W34" s="20" t="n">
+        <v>130.1</v>
+      </c>
+      <c r="X34" s="20" t="n">
+        <v>239.17</v>
       </c>
     </row>
     <row r="35">
@@ -6128,7 +6137,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -2802,15 +2802,15 @@
         <v/>
       </c>
       <c r="I35" s="17">
-        <f>IF($H35="","",IFERROR(VLOOKUP($H35,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H35="","",IFERROR(VLOOKUP($H35,PQ_Diario!$A:$D,2,0),V35))</f>
         <v/>
       </c>
       <c r="J35" s="17">
-        <f>IF($H35="","",IFERROR(VLOOKUP($H35,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H35="","",IFERROR(VLOOKUP($H35,PQ_Diario!$A:$D,3,0),W35))</f>
         <v/>
       </c>
       <c r="K35" s="17">
-        <f>IF($H35="","",IFERROR(VLOOKUP($H35,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H35="","",IFERROR(VLOOKUP($H35,PQ_Diario!$A:$D,4,0),X35))</f>
         <v/>
       </c>
       <c r="S35" s="19" t="n">
@@ -2821,6 +2821,15 @@
       </c>
       <c r="U35" s="19" t="n">
         <v>0.07488</v>
+      </c>
+      <c r="V35" s="20" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="W35" s="20" t="n">
+        <v>164.98</v>
+      </c>
+      <c r="X35" s="20" t="n">
+        <v>261.03</v>
       </c>
     </row>
     <row r="36">
@@ -3385,15 +3394,15 @@
         <v>46266</v>
       </c>
       <c r="B50" s="14">
-        <f>IFERROR(VLOOKUP($A50,PQ_Mensual!$A:$D,2,0),"")</f>
+        <f>IFERROR(VLOOKUP($A50,PQ_Mensual!$A:$D,2,0),S50)</f>
         <v/>
       </c>
       <c r="C50" s="14">
-        <f>IFERROR(VLOOKUP($A50,PQ_Mensual!$A:$D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP($A50,PQ_Mensual!$A:$D,3,0),T50)</f>
         <v/>
       </c>
       <c r="D50" s="14">
-        <f>IFERROR(VLOOKUP($A50,PQ_Mensual!$A:$D,4,0),"")</f>
+        <f>IFERROR(VLOOKUP($A50,PQ_Mensual!$A:$D,4,0),U50)</f>
         <v/>
       </c>
       <c r="E50" s="14">
@@ -3403,6 +3412,15 @@
       <c r="F50" s="15">
         <f>IF(E50="","",E50*1000)</f>
         <v/>
+      </c>
+      <c r="S50" s="19" t="n">
+        <v>0.13384</v>
+      </c>
+      <c r="T50" s="19" t="n">
+        <v>0.12727</v>
+      </c>
+      <c r="U50" s="19" t="n">
+        <v>0.1554</v>
       </c>
     </row>
     <row r="51">
@@ -5611,16 +5629,16 @@
       <c r="B50" s="28" t="n"/>
       <c r="C50" s="28" t="n"/>
       <c r="D50" s="14">
-        <f>IFERROR(VLOOKUP($A50,PQ_Mensual6P!$A:$G,4,0),"")</f>
+        <f>IFERROR(VLOOKUP($A50,PQ_Mensual6P!$A:$G,4,0),U50)</f>
         <v/>
       </c>
       <c r="E50" s="14">
-        <f>IFERROR(VLOOKUP($A50,PQ_Mensual6P!$A:$G,5,0),"")</f>
+        <f>IFERROR(VLOOKUP($A50,PQ_Mensual6P!$A:$G,5,0),V50)</f>
         <v/>
       </c>
       <c r="F50" s="28" t="n"/>
       <c r="G50" s="14">
-        <f>IFERROR(VLOOKUP($A50,PQ_Mensual6P!$A:$G,7,0),"")</f>
+        <f>IFERROR(VLOOKUP($A50,PQ_Mensual6P!$A:$G,7,0),X50)</f>
         <v/>
       </c>
       <c r="H50" s="15">
@@ -5631,6 +5649,15 @@
         <is>
           <t>MEDIA</t>
         </is>
+      </c>
+      <c r="U50" s="19" t="n">
+        <v>0.13791</v>
+      </c>
+      <c r="V50" s="19" t="n">
+        <v>0.12109</v>
+      </c>
+      <c r="X50" s="19" t="n">
+        <v>0.1554</v>
       </c>
     </row>
     <row r="51">
@@ -6101,7 +6128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6137,7 +6164,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6192,10 +6219,10 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>128.2</v>
+        <v>128</v>
       </c>
       <c r="E6" s="36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="37" t="inlineStr">
         <is>
@@ -6223,10 +6250,10 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>142.6</v>
+        <v>134</v>
       </c>
       <c r="E7" s="36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="37" t="inlineStr">
         <is>
@@ -6254,10 +6281,10 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>141.2</v>
+        <v>136.35</v>
       </c>
       <c r="E8" s="36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="37" t="inlineStr">
         <is>
@@ -6285,7 +6312,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>143</v>
+        <v>142.25</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6316,7 +6343,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>125.2</v>
+        <v>121.71</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6347,7 +6374,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>79.19</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6373,14 +6400,14 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>137.27</v>
+        <v>114.4</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>FTB Q4-26</t>
+          <t>FTB Q1-27</t>
         </is>
       </c>
     </row>
@@ -6399,14 +6426,14 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>115.5</v>
+        <v>60</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>FTB Q1-27</t>
+          <t>FTB Q2-27</t>
         </is>
       </c>
     </row>
@@ -6425,14 +6452,14 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>58.5</v>
+        <v>87.33</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>FTB Q2-27</t>
+          <t>FTB Q3-27</t>
         </is>
       </c>
     </row>
@@ -6451,14 +6478,14 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>84.5</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>FTB Q3-27</t>
+          <t>FTB Q4-27</t>
         </is>
       </c>
     </row>
@@ -6477,14 +6504,14 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>92.8</v>
+        <v>70.94</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>FTB Q4-27</t>
+          <t>FTB Q1-28</t>
         </is>
       </c>
     </row>
@@ -6503,21 +6530,21 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>71.44</v>
+        <v>44.45</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>FTB Q1-28</t>
+          <t>FTB Q2-28</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="32" t="inlineStr">
         <is>
-          <t>Q7</t>
+          <t>Y1</t>
         </is>
       </c>
       <c r="B18" s="33">
@@ -6529,21 +6556,21 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>44.95</v>
+        <v>88.7</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>FTB Q2-28</t>
+          <t>FTB YR-27</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="32" t="inlineStr">
         <is>
-          <t>Y1</t>
+          <t>Y2</t>
         </is>
       </c>
       <c r="B19" s="33">
@@ -6555,21 +6582,21 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>87.75</v>
+        <v>60</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>FTB YR-27</t>
+          <t>FTB YR-28</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="32" t="inlineStr">
         <is>
-          <t>Y2</t>
+          <t>Y3</t>
         </is>
       </c>
       <c r="B20" s="33">
@@ -6581,148 +6608,122 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>60.5</v>
+        <v>58</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>FTB YR-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="32" t="inlineStr">
-        <is>
-          <t>Y3</t>
-        </is>
-      </c>
-      <c r="B21" s="33">
-        <f>IFERROR(VLOOKUP($A21,PQ_OMIP!$A:$C,2,0),J21)</f>
-        <v/>
-      </c>
-      <c r="C21" s="34">
-        <f>IFERROR(VLOOKUP($A21,PQ_OMIP!$A:$C,3,0),D21)</f>
-        <v/>
-      </c>
-      <c r="D21" s="35" t="n">
-        <v>58</v>
-      </c>
-      <c r="E21" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
           <t>FTB YR-29</t>
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="25" t="inlineStr">
+        <is>
+          <t>Suma de pesos (debe ser 12)</t>
+        </is>
+      </c>
+      <c r="B22" s="38" t="n"/>
+      <c r="C22" s="39">
+        <f>SUM(E6:E20)</f>
+        <v/>
+      </c>
+      <c r="D22" s="4">
+        <f>IF(C22=12,"OK","⚠ ajusta pesos")</f>
+        <v/>
+      </c>
+    </row>
     <row r="23">
-      <c r="A23" s="25" t="inlineStr">
-        <is>
-          <t>Suma de pesos (debe ser 12)</t>
+      <c r="A23" s="40" t="inlineStr">
+        <is>
+          <t>FORWARD PRÓXIMOS 12 MESES (€/MWh)</t>
         </is>
       </c>
       <c r="B23" s="38" t="n"/>
-      <c r="C23" s="39">
-        <f>SUM(E6:E21)</f>
-        <v/>
-      </c>
-      <c r="D23" s="4">
-        <f>IF(C23=12,"OK","⚠ ajusta pesos")</f>
+      <c r="C23" s="41">
+        <f>SUMPRODUCT(C6:C20,E6:E20)/SUM(E6:E20)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="40" t="inlineStr">
-        <is>
-          <t>FORWARD PRÓXIMOS 12 MESES (€/MWh)</t>
+      <c r="A24" s="25" t="inlineStr">
+        <is>
+          <t>Peajes y ajustes (€/MWh)</t>
         </is>
       </c>
       <c r="B24" s="38" t="n"/>
-      <c r="C24" s="41">
-        <f>SUMPRODUCT(C6:C21,E6:E21)/SUM(E6:E21)</f>
-        <v/>
+      <c r="C24" s="42" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="25" t="inlineStr">
         <is>
-          <t>Peajes y ajustes (€/MWh)</t>
+          <t>Cobertura de seguridad (€/MWh)</t>
         </is>
       </c>
       <c r="B25" s="38" t="n"/>
       <c r="C25" s="42" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="25" t="inlineStr">
         <is>
-          <t>Cobertura de seguridad (€/MWh)</t>
+          <t>Precio fijo TEÓRICO hoy (€/MWh)</t>
         </is>
       </c>
       <c r="B26" s="38" t="n"/>
-      <c r="C26" s="42" t="n">
-        <v>10</v>
+      <c r="C26" s="43">
+        <f>C23+C24+C25</f>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="25" t="inlineStr">
         <is>
-          <t>Precio fijo TEÓRICO hoy (€/MWh)</t>
+          <t>Mejor fijo del catálogo — energía (€/MWh)</t>
         </is>
       </c>
       <c r="B27" s="38" t="n"/>
-      <c r="C27" s="43">
-        <f>C24+C25+C26</f>
-        <v/>
+      <c r="C27" s="42" t="n">
+        <v>109.9</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="25" t="inlineStr">
-        <is>
-          <t>Mejor fijo del catálogo — energía (€/MWh)</t>
+      <c r="A28" s="40" t="inlineStr">
+        <is>
+          <t>VENTANA DE FIJACIÓN (teórico − catálogo)</t>
         </is>
       </c>
       <c r="B28" s="38" t="n"/>
-      <c r="C28" s="42" t="n">
-        <v>109.9</v>
+      <c r="C28" s="41">
+        <f>C26-C27</f>
+        <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="40" t="inlineStr">
-        <is>
-          <t>VENTANA DE FIJACIÓN (teórico − catálogo)</t>
-        </is>
-      </c>
-      <c r="B29" s="38" t="n"/>
-      <c r="C29" s="41">
-        <f>C27-C28</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4">
-        <f>IF(C29&gt;5,"VENTANA ABIERTA: quien fija hoy compra por debajo de donde repreciará el catálogo",IF(C29&lt;-5,"El catálogo está caro frente al mercado: negociar o esperar","Neutral: catálogo alineado con el mercado"))</f>
+      <c r="A29" s="4">
+        <f>IF(C28&gt;5,"VENTANA ABIERTA: quien fija hoy compra por debajo de donde repreciará el catálogo",IF(C28&lt;-5,"El catálogo está caro frente al mercado: negociar o esperar","Neutral: catálogo alineado con el mercado"))</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A30:E30"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A29:E29"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="A2:H3"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="D4:H4"/>
     <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A22:B22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="I3" s="8">
-        <f>IFERROR(DATE(YEAR(MAX(PQ_Diario!A:A)),MONTH(MAX(PQ_Diario!A:A)),1),DATE(2026,9,1))</f>
+        <f>IFERROR(DATE(YEAR(MAX(PQ_Diario!A:A)),MONTH(MAX(PQ_Diario!A:A)),1),DATE(2026,10,1))</f>
         <v/>
       </c>
     </row>
@@ -1016,13 +1016,13 @@
         <v>0.04928</v>
       </c>
       <c r="V6" s="20" t="n">
-        <v>24.75</v>
+        <v>38.95</v>
       </c>
       <c r="W6" s="20" t="n">
-        <v>141.55</v>
+        <v>152.01</v>
       </c>
       <c r="X6" s="20" t="n">
-        <v>238.74</v>
+        <v>258.32</v>
       </c>
     </row>
     <row r="7">
@@ -1083,13 +1083,13 @@
         <v>0.12311</v>
       </c>
       <c r="V7" s="20" t="n">
-        <v>58.23</v>
+        <v>112.5</v>
       </c>
       <c r="W7" s="20" t="n">
-        <v>159.91</v>
+        <v>177.72</v>
       </c>
       <c r="X7" s="20" t="n">
-        <v>247.27</v>
+        <v>279.83</v>
       </c>
     </row>
     <row r="8">
@@ -1121,15 +1121,15 @@
         <v/>
       </c>
       <c r="I8" s="17">
-        <f>IF($H8="","",IFERROR(VLOOKUP($H8,PQ_Diario!$A:$D,2,0),V8))</f>
+        <f>IF($H8="","",IFERROR(VLOOKUP($H8,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J8" s="17">
-        <f>IF($H8="","",IFERROR(VLOOKUP($H8,PQ_Diario!$A:$D,3,0),W8))</f>
+        <f>IF($H8="","",IFERROR(VLOOKUP($H8,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K8" s="17">
-        <f>IF($H8="","",IFERROR(VLOOKUP($H8,PQ_Diario!$A:$D,4,0),X8))</f>
+        <f>IF($H8="","",IFERROR(VLOOKUP($H8,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="Q8" s="18">
@@ -1148,15 +1148,6 @@
       </c>
       <c r="U8" s="19" t="n">
         <v>0.08814</v>
-      </c>
-      <c r="V8" s="20" t="n">
-        <v>27</v>
-      </c>
-      <c r="W8" s="20" t="n">
-        <v>155.99</v>
-      </c>
-      <c r="X8" s="20" t="n">
-        <v>300</v>
       </c>
     </row>
     <row r="9">
@@ -1188,15 +1179,15 @@
         <v/>
       </c>
       <c r="I9" s="17">
-        <f>IF($H9="","",IFERROR(VLOOKUP($H9,PQ_Diario!$A:$D,2,0),V9))</f>
+        <f>IF($H9="","",IFERROR(VLOOKUP($H9,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J9" s="17">
-        <f>IF($H9="","",IFERROR(VLOOKUP($H9,PQ_Diario!$A:$D,3,0),W9))</f>
+        <f>IF($H9="","",IFERROR(VLOOKUP($H9,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K9" s="17">
-        <f>IF($H9="","",IFERROR(VLOOKUP($H9,PQ_Diario!$A:$D,4,0),X9))</f>
+        <f>IF($H9="","",IFERROR(VLOOKUP($H9,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="Q9" s="18">
@@ -1215,15 +1206,6 @@
       </c>
       <c r="U9" s="19" t="n">
         <v>0.07088</v>
-      </c>
-      <c r="V9" s="20" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="W9" s="20" t="n">
-        <v>169.5</v>
-      </c>
-      <c r="X9" s="20" t="n">
-        <v>260.27</v>
       </c>
     </row>
     <row r="10">
@@ -1255,15 +1237,15 @@
         <v/>
       </c>
       <c r="I10" s="17">
-        <f>IF($H10="","",IFERROR(VLOOKUP($H10,PQ_Diario!$A:$D,2,0),V10))</f>
+        <f>IF($H10="","",IFERROR(VLOOKUP($H10,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J10" s="17">
-        <f>IF($H10="","",IFERROR(VLOOKUP($H10,PQ_Diario!$A:$D,3,0),W10))</f>
+        <f>IF($H10="","",IFERROR(VLOOKUP($H10,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K10" s="17">
-        <f>IF($H10="","",IFERROR(VLOOKUP($H10,PQ_Diario!$A:$D,4,0),X10))</f>
+        <f>IF($H10="","",IFERROR(VLOOKUP($H10,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="Q10" s="18">
@@ -1282,15 +1264,6 @@
       </c>
       <c r="U10" s="19" t="n">
         <v>0.07295</v>
-      </c>
-      <c r="V10" s="20" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="W10" s="20" t="n">
-        <v>138.11</v>
-      </c>
-      <c r="X10" s="20" t="n">
-        <v>225.01</v>
       </c>
     </row>
     <row r="11">
@@ -1322,15 +1295,15 @@
         <v/>
       </c>
       <c r="I11" s="17">
-        <f>IF($H11="","",IFERROR(VLOOKUP($H11,PQ_Diario!$A:$D,2,0),V11))</f>
+        <f>IF($H11="","",IFERROR(VLOOKUP($H11,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J11" s="17">
-        <f>IF($H11="","",IFERROR(VLOOKUP($H11,PQ_Diario!$A:$D,3,0),W11))</f>
+        <f>IF($H11="","",IFERROR(VLOOKUP($H11,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K11" s="17">
-        <f>IF($H11="","",IFERROR(VLOOKUP($H11,PQ_Diario!$A:$D,4,0),X11))</f>
+        <f>IF($H11="","",IFERROR(VLOOKUP($H11,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="Q11" s="18">
@@ -1349,15 +1322,6 @@
       </c>
       <c r="U11" s="19" t="n">
         <v>0.08851000000000001</v>
-      </c>
-      <c r="V11" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" s="20" t="n">
-        <v>140.01</v>
-      </c>
-      <c r="X11" s="20" t="n">
-        <v>249.3</v>
       </c>
     </row>
     <row r="12">
@@ -1389,15 +1353,15 @@
         <v/>
       </c>
       <c r="I12" s="17">
-        <f>IF($H12="","",IFERROR(VLOOKUP($H12,PQ_Diario!$A:$D,2,0),V12))</f>
+        <f>IF($H12="","",IFERROR(VLOOKUP($H12,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J12" s="17">
-        <f>IF($H12="","",IFERROR(VLOOKUP($H12,PQ_Diario!$A:$D,3,0),W12))</f>
+        <f>IF($H12="","",IFERROR(VLOOKUP($H12,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K12" s="17">
-        <f>IF($H12="","",IFERROR(VLOOKUP($H12,PQ_Diario!$A:$D,4,0),X12))</f>
+        <f>IF($H12="","",IFERROR(VLOOKUP($H12,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="Q12" s="18">
@@ -1416,15 +1380,6 @@
       </c>
       <c r="U12" s="19" t="n">
         <v>0.08432000000000001</v>
-      </c>
-      <c r="V12" s="20" t="n">
-        <v>57</v>
-      </c>
-      <c r="W12" s="20" t="n">
-        <v>172.07</v>
-      </c>
-      <c r="X12" s="20" t="n">
-        <v>265</v>
       </c>
     </row>
     <row r="13">
@@ -1456,15 +1411,15 @@
         <v/>
       </c>
       <c r="I13" s="17">
-        <f>IF($H13="","",IFERROR(VLOOKUP($H13,PQ_Diario!$A:$D,2,0),V13))</f>
+        <f>IF($H13="","",IFERROR(VLOOKUP($H13,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J13" s="17">
-        <f>IF($H13="","",IFERROR(VLOOKUP($H13,PQ_Diario!$A:$D,3,0),W13))</f>
+        <f>IF($H13="","",IFERROR(VLOOKUP($H13,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K13" s="17">
-        <f>IF($H13="","",IFERROR(VLOOKUP($H13,PQ_Diario!$A:$D,4,0),X13))</f>
+        <f>IF($H13="","",IFERROR(VLOOKUP($H13,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="Q13" s="18">
@@ -1483,15 +1438,6 @@
       </c>
       <c r="U13" s="19" t="n">
         <v>0.09261</v>
-      </c>
-      <c r="V13" s="20" t="n">
-        <v>33.62</v>
-      </c>
-      <c r="W13" s="20" t="n">
-        <v>151.73</v>
-      </c>
-      <c r="X13" s="20" t="n">
-        <v>230.01</v>
       </c>
     </row>
     <row r="14">
@@ -1523,15 +1469,15 @@
         <v/>
       </c>
       <c r="I14" s="17">
-        <f>IF($H14="","",IFERROR(VLOOKUP($H14,PQ_Diario!$A:$D,2,0),V14))</f>
+        <f>IF($H14="","",IFERROR(VLOOKUP($H14,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J14" s="17">
-        <f>IF($H14="","",IFERROR(VLOOKUP($H14,PQ_Diario!$A:$D,3,0),W14))</f>
+        <f>IF($H14="","",IFERROR(VLOOKUP($H14,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K14" s="17">
-        <f>IF($H14="","",IFERROR(VLOOKUP($H14,PQ_Diario!$A:$D,4,0),X14))</f>
+        <f>IF($H14="","",IFERROR(VLOOKUP($H14,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="Q14" s="18">
@@ -1550,15 +1496,6 @@
       </c>
       <c r="U14" s="19" t="n">
         <v>0.09848</v>
-      </c>
-      <c r="V14" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" s="20" t="n">
-        <v>107.76</v>
-      </c>
-      <c r="X14" s="20" t="n">
-        <v>212.09</v>
       </c>
     </row>
     <row r="15">
@@ -1590,15 +1527,15 @@
         <v/>
       </c>
       <c r="I15" s="17">
-        <f>IF($H15="","",IFERROR(VLOOKUP($H15,PQ_Diario!$A:$D,2,0),V15))</f>
+        <f>IF($H15="","",IFERROR(VLOOKUP($H15,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J15" s="17">
-        <f>IF($H15="","",IFERROR(VLOOKUP($H15,PQ_Diario!$A:$D,3,0),W15))</f>
+        <f>IF($H15="","",IFERROR(VLOOKUP($H15,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K15" s="17">
-        <f>IF($H15="","",IFERROR(VLOOKUP($H15,PQ_Diario!$A:$D,4,0),X15))</f>
+        <f>IF($H15="","",IFERROR(VLOOKUP($H15,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="Q15" s="18">
@@ -1617,15 +1554,6 @@
       </c>
       <c r="U15" s="19" t="n">
         <v>0.08542</v>
-      </c>
-      <c r="V15" s="20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W15" s="20" t="n">
-        <v>145.21</v>
-      </c>
-      <c r="X15" s="20" t="n">
-        <v>278.48</v>
       </c>
     </row>
     <row r="16">
@@ -1657,15 +1585,15 @@
         <v/>
       </c>
       <c r="I16" s="17">
-        <f>IF($H16="","",IFERROR(VLOOKUP($H16,PQ_Diario!$A:$D,2,0),V16))</f>
+        <f>IF($H16="","",IFERROR(VLOOKUP($H16,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J16" s="17">
-        <f>IF($H16="","",IFERROR(VLOOKUP($H16,PQ_Diario!$A:$D,3,0),W16))</f>
+        <f>IF($H16="","",IFERROR(VLOOKUP($H16,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K16" s="17">
-        <f>IF($H16="","",IFERROR(VLOOKUP($H16,PQ_Diario!$A:$D,4,0),X16))</f>
+        <f>IF($H16="","",IFERROR(VLOOKUP($H16,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="Q16" s="18">
@@ -1684,15 +1612,6 @@
       </c>
       <c r="U16" s="19" t="n">
         <v>0.05176</v>
-      </c>
-      <c r="V16" s="20" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="W16" s="20" t="n">
-        <v>144.5</v>
-      </c>
-      <c r="X16" s="20" t="n">
-        <v>250.01</v>
       </c>
     </row>
     <row r="17">
@@ -1724,15 +1643,15 @@
         <v/>
       </c>
       <c r="I17" s="17">
-        <f>IF($H17="","",IFERROR(VLOOKUP($H17,PQ_Diario!$A:$D,2,0),V17))</f>
+        <f>IF($H17="","",IFERROR(VLOOKUP($H17,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J17" s="17">
-        <f>IF($H17="","",IFERROR(VLOOKUP($H17,PQ_Diario!$A:$D,3,0),W17))</f>
+        <f>IF($H17="","",IFERROR(VLOOKUP($H17,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K17" s="17">
-        <f>IF($H17="","",IFERROR(VLOOKUP($H17,PQ_Diario!$A:$D,4,0),X17))</f>
+        <f>IF($H17="","",IFERROR(VLOOKUP($H17,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="Q17" s="18">
@@ -1751,15 +1670,6 @@
       </c>
       <c r="U17" s="19" t="n">
         <v>0.06365</v>
-      </c>
-      <c r="V17" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" s="20" t="n">
-        <v>118.28</v>
-      </c>
-      <c r="X17" s="20" t="n">
-        <v>213.63</v>
       </c>
     </row>
     <row r="18">
@@ -1791,15 +1701,15 @@
         <v/>
       </c>
       <c r="I18" s="17">
-        <f>IF($H18="","",IFERROR(VLOOKUP($H18,PQ_Diario!$A:$D,2,0),V18))</f>
+        <f>IF($H18="","",IFERROR(VLOOKUP($H18,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J18" s="17">
-        <f>IF($H18="","",IFERROR(VLOOKUP($H18,PQ_Diario!$A:$D,3,0),W18))</f>
+        <f>IF($H18="","",IFERROR(VLOOKUP($H18,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K18" s="17">
-        <f>IF($H18="","",IFERROR(VLOOKUP($H18,PQ_Diario!$A:$D,4,0),X18))</f>
+        <f>IF($H18="","",IFERROR(VLOOKUP($H18,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="Q18" s="21">
@@ -1818,15 +1728,6 @@
       </c>
       <c r="U18" s="19" t="n">
         <v>0.06423</v>
-      </c>
-      <c r="V18" s="20" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="W18" s="20" t="n">
-        <v>121.39</v>
-      </c>
-      <c r="X18" s="20" t="n">
-        <v>237.53</v>
       </c>
     </row>
     <row r="19">
@@ -1858,15 +1759,15 @@
         <v/>
       </c>
       <c r="I19" s="17">
-        <f>IF($H19="","",IFERROR(VLOOKUP($H19,PQ_Diario!$A:$D,2,0),V19))</f>
+        <f>IF($H19="","",IFERROR(VLOOKUP($H19,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J19" s="17">
-        <f>IF($H19="","",IFERROR(VLOOKUP($H19,PQ_Diario!$A:$D,3,0),W19))</f>
+        <f>IF($H19="","",IFERROR(VLOOKUP($H19,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K19" s="17">
-        <f>IF($H19="","",IFERROR(VLOOKUP($H19,PQ_Diario!$A:$D,4,0),X19))</f>
+        <f>IF($H19="","",IFERROR(VLOOKUP($H19,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="S19" s="19" t="n">
@@ -1877,15 +1778,6 @@
       </c>
       <c r="U19" s="19" t="n">
         <v>0.03621</v>
-      </c>
-      <c r="V19" s="20" t="n">
-        <v>40.53</v>
-      </c>
-      <c r="W19" s="20" t="n">
-        <v>177.44</v>
-      </c>
-      <c r="X19" s="20" t="n">
-        <v>300</v>
       </c>
     </row>
     <row r="20">
@@ -1917,15 +1809,15 @@
         <v/>
       </c>
       <c r="I20" s="17">
-        <f>IF($H20="","",IFERROR(VLOOKUP($H20,PQ_Diario!$A:$D,2,0),V20))</f>
+        <f>IF($H20="","",IFERROR(VLOOKUP($H20,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J20" s="17">
-        <f>IF($H20="","",IFERROR(VLOOKUP($H20,PQ_Diario!$A:$D,3,0),W20))</f>
+        <f>IF($H20="","",IFERROR(VLOOKUP($H20,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K20" s="17">
-        <f>IF($H20="","",IFERROR(VLOOKUP($H20,PQ_Diario!$A:$D,4,0),X20))</f>
+        <f>IF($H20="","",IFERROR(VLOOKUP($H20,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="S20" s="19" t="n">
@@ -1936,15 +1828,6 @@
       </c>
       <c r="U20" s="19" t="n">
         <v>0.01494</v>
-      </c>
-      <c r="V20" s="20" t="n">
-        <v>35.67</v>
-      </c>
-      <c r="W20" s="20" t="n">
-        <v>167.33</v>
-      </c>
-      <c r="X20" s="20" t="n">
-        <v>268.06</v>
       </c>
     </row>
     <row r="21">
@@ -1976,15 +1859,15 @@
         <v/>
       </c>
       <c r="I21" s="17">
-        <f>IF($H21="","",IFERROR(VLOOKUP($H21,PQ_Diario!$A:$D,2,0),V21))</f>
+        <f>IF($H21="","",IFERROR(VLOOKUP($H21,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J21" s="17">
-        <f>IF($H21="","",IFERROR(VLOOKUP($H21,PQ_Diario!$A:$D,3,0),W21))</f>
+        <f>IF($H21="","",IFERROR(VLOOKUP($H21,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K21" s="17">
-        <f>IF($H21="","",IFERROR(VLOOKUP($H21,PQ_Diario!$A:$D,4,0),X21))</f>
+        <f>IF($H21="","",IFERROR(VLOOKUP($H21,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="S21" s="19" t="n">
@@ -1995,15 +1878,6 @@
       </c>
       <c r="U21" s="19" t="n">
         <v>0.01337</v>
-      </c>
-      <c r="V21" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" s="20" t="n">
-        <v>104.63</v>
-      </c>
-      <c r="X21" s="20" t="n">
-        <v>196.18</v>
       </c>
     </row>
     <row r="22">
@@ -2035,15 +1909,15 @@
         <v/>
       </c>
       <c r="I22" s="17">
-        <f>IF($H22="","",IFERROR(VLOOKUP($H22,PQ_Diario!$A:$D,2,0),V22))</f>
+        <f>IF($H22="","",IFERROR(VLOOKUP($H22,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J22" s="17">
-        <f>IF($H22="","",IFERROR(VLOOKUP($H22,PQ_Diario!$A:$D,3,0),W22))</f>
+        <f>IF($H22="","",IFERROR(VLOOKUP($H22,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K22" s="17">
-        <f>IF($H22="","",IFERROR(VLOOKUP($H22,PQ_Diario!$A:$D,4,0),X22))</f>
+        <f>IF($H22="","",IFERROR(VLOOKUP($H22,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="S22" s="19" t="n">
@@ -2054,15 +1928,6 @@
       </c>
       <c r="U22" s="19" t="n">
         <v>0.03306</v>
-      </c>
-      <c r="V22" s="20" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="W22" s="20" t="n">
-        <v>127.41</v>
-      </c>
-      <c r="X22" s="20" t="n">
-        <v>244.11</v>
       </c>
     </row>
     <row r="23">
@@ -2094,15 +1959,15 @@
         <v/>
       </c>
       <c r="I23" s="17">
-        <f>IF($H23="","",IFERROR(VLOOKUP($H23,PQ_Diario!$A:$D,2,0),V23))</f>
+        <f>IF($H23="","",IFERROR(VLOOKUP($H23,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J23" s="17">
-        <f>IF($H23="","",IFERROR(VLOOKUP($H23,PQ_Diario!$A:$D,3,0),W23))</f>
+        <f>IF($H23="","",IFERROR(VLOOKUP($H23,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K23" s="17">
-        <f>IF($H23="","",IFERROR(VLOOKUP($H23,PQ_Diario!$A:$D,4,0),X23))</f>
+        <f>IF($H23="","",IFERROR(VLOOKUP($H23,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="S23" s="19" t="n">
@@ -2113,15 +1978,6 @@
       </c>
       <c r="U23" s="19" t="n">
         <v>0.05189</v>
-      </c>
-      <c r="V23" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" s="20" t="n">
-        <v>124.78</v>
-      </c>
-      <c r="X23" s="20" t="n">
-        <v>228.78</v>
       </c>
     </row>
     <row r="24">
@@ -2153,15 +2009,15 @@
         <v/>
       </c>
       <c r="I24" s="17">
-        <f>IF($H24="","",IFERROR(VLOOKUP($H24,PQ_Diario!$A:$D,2,0),V24))</f>
+        <f>IF($H24="","",IFERROR(VLOOKUP($H24,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J24" s="17">
-        <f>IF($H24="","",IFERROR(VLOOKUP($H24,PQ_Diario!$A:$D,3,0),W24))</f>
+        <f>IF($H24="","",IFERROR(VLOOKUP($H24,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K24" s="17">
-        <f>IF($H24="","",IFERROR(VLOOKUP($H24,PQ_Diario!$A:$D,4,0),X24))</f>
+        <f>IF($H24="","",IFERROR(VLOOKUP($H24,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="S24" s="19" t="n">
@@ -2172,15 +2028,6 @@
       </c>
       <c r="U24" s="19" t="n">
         <v>0.07045</v>
-      </c>
-      <c r="V24" s="20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W24" s="20" t="n">
-        <v>110.26</v>
-      </c>
-      <c r="X24" s="20" t="n">
-        <v>201.15</v>
       </c>
     </row>
     <row r="25">
@@ -2212,15 +2059,15 @@
         <v/>
       </c>
       <c r="I25" s="17">
-        <f>IF($H25="","",IFERROR(VLOOKUP($H25,PQ_Diario!$A:$D,2,0),V25))</f>
+        <f>IF($H25="","",IFERROR(VLOOKUP($H25,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J25" s="17">
-        <f>IF($H25="","",IFERROR(VLOOKUP($H25,PQ_Diario!$A:$D,3,0),W25))</f>
+        <f>IF($H25="","",IFERROR(VLOOKUP($H25,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K25" s="17">
-        <f>IF($H25="","",IFERROR(VLOOKUP($H25,PQ_Diario!$A:$D,4,0),X25))</f>
+        <f>IF($H25="","",IFERROR(VLOOKUP($H25,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="S25" s="19" t="n">
@@ -2231,15 +2078,6 @@
       </c>
       <c r="U25" s="19" t="n">
         <v>0.08558</v>
-      </c>
-      <c r="V25" s="20" t="n">
-        <v>-1.14</v>
-      </c>
-      <c r="W25" s="20" t="n">
-        <v>112.56</v>
-      </c>
-      <c r="X25" s="20" t="n">
-        <v>225.57</v>
       </c>
     </row>
     <row r="26">
@@ -2271,15 +2109,15 @@
         <v/>
       </c>
       <c r="I26" s="17">
-        <f>IF($H26="","",IFERROR(VLOOKUP($H26,PQ_Diario!$A:$D,2,0),V26))</f>
+        <f>IF($H26="","",IFERROR(VLOOKUP($H26,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J26" s="17">
-        <f>IF($H26="","",IFERROR(VLOOKUP($H26,PQ_Diario!$A:$D,3,0),W26))</f>
+        <f>IF($H26="","",IFERROR(VLOOKUP($H26,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K26" s="17">
-        <f>IF($H26="","",IFERROR(VLOOKUP($H26,PQ_Diario!$A:$D,4,0),X26))</f>
+        <f>IF($H26="","",IFERROR(VLOOKUP($H26,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="S26" s="19" t="n">
@@ -2290,15 +2128,6 @@
       </c>
       <c r="U26" s="19" t="n">
         <v>0.0725</v>
-      </c>
-      <c r="V26" s="20" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="W26" s="20" t="n">
-        <v>138.77</v>
-      </c>
-      <c r="X26" s="20" t="n">
-        <v>276.54</v>
       </c>
     </row>
     <row r="27">
@@ -2330,15 +2159,15 @@
         <v/>
       </c>
       <c r="I27" s="17">
-        <f>IF($H27="","",IFERROR(VLOOKUP($H27,PQ_Diario!$A:$D,2,0),V27))</f>
+        <f>IF($H27="","",IFERROR(VLOOKUP($H27,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J27" s="17">
-        <f>IF($H27="","",IFERROR(VLOOKUP($H27,PQ_Diario!$A:$D,3,0),W27))</f>
+        <f>IF($H27="","",IFERROR(VLOOKUP($H27,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K27" s="17">
-        <f>IF($H27="","",IFERROR(VLOOKUP($H27,PQ_Diario!$A:$D,4,0),X27))</f>
+        <f>IF($H27="","",IFERROR(VLOOKUP($H27,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="S27" s="19" t="n">
@@ -2349,15 +2178,6 @@
       </c>
       <c r="U27" s="19" t="n">
         <v>0.0595</v>
-      </c>
-      <c r="V27" s="20" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="W27" s="20" t="n">
-        <v>156.02</v>
-      </c>
-      <c r="X27" s="20" t="n">
-        <v>300</v>
       </c>
     </row>
     <row r="28">
@@ -2389,15 +2209,15 @@
         <v/>
       </c>
       <c r="I28" s="17">
-        <f>IF($H28="","",IFERROR(VLOOKUP($H28,PQ_Diario!$A:$D,2,0),V28))</f>
+        <f>IF($H28="","",IFERROR(VLOOKUP($H28,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J28" s="17">
-        <f>IF($H28="","",IFERROR(VLOOKUP($H28,PQ_Diario!$A:$D,3,0),W28))</f>
+        <f>IF($H28="","",IFERROR(VLOOKUP($H28,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K28" s="17">
-        <f>IF($H28="","",IFERROR(VLOOKUP($H28,PQ_Diario!$A:$D,4,0),X28))</f>
+        <f>IF($H28="","",IFERROR(VLOOKUP($H28,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="S28" s="19" t="n">
@@ -2408,15 +2228,6 @@
       </c>
       <c r="U28" s="19" t="n">
         <v>0.09408999999999999</v>
-      </c>
-      <c r="V28" s="20" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="W28" s="20" t="n">
-        <v>158.88</v>
-      </c>
-      <c r="X28" s="20" t="n">
-        <v>274.36</v>
       </c>
     </row>
     <row r="29">
@@ -2448,15 +2259,15 @@
         <v/>
       </c>
       <c r="I29" s="17">
-        <f>IF($H29="","",IFERROR(VLOOKUP($H29,PQ_Diario!$A:$D,2,0),V29))</f>
+        <f>IF($H29="","",IFERROR(VLOOKUP($H29,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J29" s="17">
-        <f>IF($H29="","",IFERROR(VLOOKUP($H29,PQ_Diario!$A:$D,3,0),W29))</f>
+        <f>IF($H29="","",IFERROR(VLOOKUP($H29,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K29" s="17">
-        <f>IF($H29="","",IFERROR(VLOOKUP($H29,PQ_Diario!$A:$D,4,0),X29))</f>
+        <f>IF($H29="","",IFERROR(VLOOKUP($H29,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="S29" s="19" t="n">
@@ -2467,15 +2278,6 @@
       </c>
       <c r="U29" s="19" t="n">
         <v>0.10005</v>
-      </c>
-      <c r="V29" s="20" t="n">
-        <v>17.62</v>
-      </c>
-      <c r="W29" s="20" t="n">
-        <v>157.24</v>
-      </c>
-      <c r="X29" s="20" t="n">
-        <v>288.23</v>
       </c>
     </row>
     <row r="30">
@@ -2507,15 +2309,15 @@
         <v/>
       </c>
       <c r="I30" s="17">
-        <f>IF($H30="","",IFERROR(VLOOKUP($H30,PQ_Diario!$A:$D,2,0),V30))</f>
+        <f>IF($H30="","",IFERROR(VLOOKUP($H30,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J30" s="17">
-        <f>IF($H30="","",IFERROR(VLOOKUP($H30,PQ_Diario!$A:$D,3,0),W30))</f>
+        <f>IF($H30="","",IFERROR(VLOOKUP($H30,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K30" s="17">
-        <f>IF($H30="","",IFERROR(VLOOKUP($H30,PQ_Diario!$A:$D,4,0),X30))</f>
+        <f>IF($H30="","",IFERROR(VLOOKUP($H30,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="S30" s="19" t="n">
@@ -2526,15 +2328,6 @@
       </c>
       <c r="U30" s="19" t="n">
         <v>0.08304</v>
-      </c>
-      <c r="V30" s="20" t="n">
-        <v>19.17</v>
-      </c>
-      <c r="W30" s="20" t="n">
-        <v>158.92</v>
-      </c>
-      <c r="X30" s="20" t="n">
-        <v>287.13</v>
       </c>
     </row>
     <row r="31">
@@ -2566,15 +2359,15 @@
         <v/>
       </c>
       <c r="I31" s="17">
-        <f>IF($H31="","",IFERROR(VLOOKUP($H31,PQ_Diario!$A:$D,2,0),V31))</f>
+        <f>IF($H31="","",IFERROR(VLOOKUP($H31,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J31" s="17">
-        <f>IF($H31="","",IFERROR(VLOOKUP($H31,PQ_Diario!$A:$D,3,0),W31))</f>
+        <f>IF($H31="","",IFERROR(VLOOKUP($H31,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K31" s="17">
-        <f>IF($H31="","",IFERROR(VLOOKUP($H31,PQ_Diario!$A:$D,4,0),X31))</f>
+        <f>IF($H31="","",IFERROR(VLOOKUP($H31,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="S31" s="19" t="n">
@@ -2585,15 +2378,6 @@
       </c>
       <c r="U31" s="19" t="n">
         <v>0.10093</v>
-      </c>
-      <c r="V31" s="20" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="W31" s="20" t="n">
-        <v>130.62</v>
-      </c>
-      <c r="X31" s="20" t="n">
-        <v>251.08</v>
       </c>
     </row>
     <row r="32">
@@ -2625,15 +2409,15 @@
         <v/>
       </c>
       <c r="I32" s="17">
-        <f>IF($H32="","",IFERROR(VLOOKUP($H32,PQ_Diario!$A:$D,2,0),V32))</f>
+        <f>IF($H32="","",IFERROR(VLOOKUP($H32,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J32" s="17">
-        <f>IF($H32="","",IFERROR(VLOOKUP($H32,PQ_Diario!$A:$D,3,0),W32))</f>
+        <f>IF($H32="","",IFERROR(VLOOKUP($H32,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K32" s="17">
-        <f>IF($H32="","",IFERROR(VLOOKUP($H32,PQ_Diario!$A:$D,4,0),X32))</f>
+        <f>IF($H32="","",IFERROR(VLOOKUP($H32,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="S32" s="19" t="n">
@@ -2644,15 +2428,6 @@
       </c>
       <c r="U32" s="19" t="n">
         <v>0.04494</v>
-      </c>
-      <c r="V32" s="20" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="W32" s="20" t="n">
-        <v>113.65</v>
-      </c>
-      <c r="X32" s="20" t="n">
-        <v>210.26</v>
       </c>
     </row>
     <row r="33">
@@ -2684,15 +2459,15 @@
         <v/>
       </c>
       <c r="I33" s="17">
-        <f>IF($H33="","",IFERROR(VLOOKUP($H33,PQ_Diario!$A:$D,2,0),V33))</f>
+        <f>IF($H33="","",IFERROR(VLOOKUP($H33,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J33" s="17">
-        <f>IF($H33="","",IFERROR(VLOOKUP($H33,PQ_Diario!$A:$D,3,0),W33))</f>
+        <f>IF($H33="","",IFERROR(VLOOKUP($H33,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K33" s="17">
-        <f>IF($H33="","",IFERROR(VLOOKUP($H33,PQ_Diario!$A:$D,4,0),X33))</f>
+        <f>IF($H33="","",IFERROR(VLOOKUP($H33,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="S33" s="19" t="n">
@@ -2703,15 +2478,6 @@
       </c>
       <c r="U33" s="19" t="n">
         <v>0.02598</v>
-      </c>
-      <c r="V33" s="20" t="n">
-        <v>147.32</v>
-      </c>
-      <c r="W33" s="20" t="n">
-        <v>198.05</v>
-      </c>
-      <c r="X33" s="20" t="n">
-        <v>280.59</v>
       </c>
     </row>
     <row r="34">
@@ -2743,15 +2509,15 @@
         <v/>
       </c>
       <c r="I34" s="17">
-        <f>IF($H34="","",IFERROR(VLOOKUP($H34,PQ_Diario!$A:$D,2,0),V34))</f>
+        <f>IF($H34="","",IFERROR(VLOOKUP($H34,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J34" s="17">
-        <f>IF($H34="","",IFERROR(VLOOKUP($H34,PQ_Diario!$A:$D,3,0),W34))</f>
+        <f>IF($H34="","",IFERROR(VLOOKUP($H34,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K34" s="17">
-        <f>IF($H34="","",IFERROR(VLOOKUP($H34,PQ_Diario!$A:$D,4,0),X34))</f>
+        <f>IF($H34="","",IFERROR(VLOOKUP($H34,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="S34" s="19" t="n">
@@ -2762,15 +2528,6 @@
       </c>
       <c r="U34" s="19" t="n">
         <v>0.01711</v>
-      </c>
-      <c r="V34" s="20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W34" s="20" t="n">
-        <v>130.1</v>
-      </c>
-      <c r="X34" s="20" t="n">
-        <v>239.17</v>
       </c>
     </row>
     <row r="35">
@@ -2802,15 +2559,15 @@
         <v/>
       </c>
       <c r="I35" s="17">
-        <f>IF($H35="","",IFERROR(VLOOKUP($H35,PQ_Diario!$A:$D,2,0),V35))</f>
+        <f>IF($H35="","",IFERROR(VLOOKUP($H35,PQ_Diario!$A:$D,2,0),""))</f>
         <v/>
       </c>
       <c r="J35" s="17">
-        <f>IF($H35="","",IFERROR(VLOOKUP($H35,PQ_Diario!$A:$D,3,0),W35))</f>
+        <f>IF($H35="","",IFERROR(VLOOKUP($H35,PQ_Diario!$A:$D,3,0),""))</f>
         <v/>
       </c>
       <c r="K35" s="17">
-        <f>IF($H35="","",IFERROR(VLOOKUP($H35,PQ_Diario!$A:$D,4,0),X35))</f>
+        <f>IF($H35="","",IFERROR(VLOOKUP($H35,PQ_Diario!$A:$D,4,0),""))</f>
         <v/>
       </c>
       <c r="S35" s="19" t="n">
@@ -2821,15 +2578,6 @@
       </c>
       <c r="U35" s="19" t="n">
         <v>0.07488</v>
-      </c>
-      <c r="V35" s="20" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="W35" s="20" t="n">
-        <v>164.98</v>
-      </c>
-      <c r="X35" s="20" t="n">
-        <v>261.03</v>
       </c>
     </row>
     <row r="36">
@@ -6128,7 +5876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6164,7 +5912,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6219,7 +5967,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>128</v>
+        <v>138.8</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>1</v>
@@ -6231,7 +5979,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>FTB M Oct-26</t>
+          <t>FTB M Nov-26</t>
         </is>
       </c>
     </row>
@@ -6250,7 +5998,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>1</v>
@@ -6262,7 +6010,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>FTB M Nov-26</t>
+          <t>FTB M Dec-26</t>
         </is>
       </c>
     </row>
@@ -6281,10 +6029,10 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>136.35</v>
+        <v>145.85</v>
       </c>
       <c r="E8" s="36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="37" t="inlineStr">
         <is>
@@ -6293,7 +6041,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>FTB M Dec-26</t>
+          <t>FTB M Jan-27</t>
         </is>
       </c>
     </row>
@@ -6312,7 +6060,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>142.25</v>
+        <v>125.31</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6324,7 +6072,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>FTB M Jan-27</t>
+          <t>FTB M Feb-27</t>
         </is>
       </c>
     </row>
@@ -6343,7 +6091,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>121.71</v>
+        <v>83.5</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6355,7 +6103,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>FTB M Feb-27</t>
+          <t>FTB M Mar-27</t>
         </is>
       </c>
     </row>
@@ -6374,14 +6122,14 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>79.90000000000001</v>
+        <v>47.64</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>FTB M Mar-27</t>
+          <t>FTB M Apr-27</t>
         </is>
       </c>
     </row>
@@ -6400,7 +6148,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>114.4</v>
+        <v>118</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6426,7 +6174,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>60</v>
+        <v>60.75</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6452,7 +6200,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>87.33</v>
+        <v>90.70999999999999</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6478,10 +6226,10 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>93.31999999999999</v>
+        <v>95.8</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -6504,7 +6252,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>70.94</v>
+        <v>71.44</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6530,7 +6278,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>44.45</v>
+        <v>44.95</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6544,7 +6292,7 @@
     <row r="18">
       <c r="A18" s="32" t="inlineStr">
         <is>
-          <t>Y1</t>
+          <t>Q7</t>
         </is>
       </c>
       <c r="B18" s="33">
@@ -6556,21 +6304,21 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>88.7</v>
+        <v>61.5</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>FTB YR-27</t>
+          <t>FTB Q3-28</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="32" t="inlineStr">
         <is>
-          <t>Y2</t>
+          <t>Y1</t>
         </is>
       </c>
       <c r="B19" s="33">
@@ -6582,21 +6330,21 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>60</v>
+        <v>91.25</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>FTB YR-28</t>
+          <t>FTB YR-27</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="32" t="inlineStr">
         <is>
-          <t>Y3</t>
+          <t>Y2</t>
         </is>
       </c>
       <c r="B20" s="33">
@@ -6608,122 +6356,148 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>58</v>
+        <v>60.5</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t>FTB YR-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="32" t="inlineStr">
+        <is>
+          <t>Y3</t>
+        </is>
+      </c>
+      <c r="B21" s="33">
+        <f>IFERROR(VLOOKUP($A21,PQ_OMIP!$A:$C,2,0),J21)</f>
+        <v/>
+      </c>
+      <c r="C21" s="34">
+        <f>IFERROR(VLOOKUP($A21,PQ_OMIP!$A:$C,3,0),D21)</f>
+        <v/>
+      </c>
+      <c r="D21" s="35" t="n">
+        <v>57.65</v>
+      </c>
+      <c r="E21" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
           <t>FTB YR-29</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="25" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="25" t="inlineStr">
         <is>
           <t>Suma de pesos (debe ser 12)</t>
         </is>
       </c>
-      <c r="B22" s="38" t="n"/>
-      <c r="C22" s="39">
-        <f>SUM(E6:E20)</f>
-        <v/>
-      </c>
-      <c r="D22" s="4">
-        <f>IF(C22=12,"OK","⚠ ajusta pesos")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="40" t="inlineStr">
+      <c r="B23" s="38" t="n"/>
+      <c r="C23" s="39">
+        <f>SUM(E6:E21)</f>
+        <v/>
+      </c>
+      <c r="D23" s="4">
+        <f>IF(C23=12,"OK","⚠ ajusta pesos")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="40" t="inlineStr">
         <is>
           <t>FORWARD PRÓXIMOS 12 MESES (€/MWh)</t>
         </is>
       </c>
-      <c r="B23" s="38" t="n"/>
-      <c r="C23" s="41">
-        <f>SUMPRODUCT(C6:C20,E6:E20)/SUM(E6:E20)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="25" t="inlineStr">
-        <is>
-          <t>Peajes y ajustes (€/MWh)</t>
-        </is>
-      </c>
       <c r="B24" s="38" t="n"/>
-      <c r="C24" s="42" t="n">
-        <v>28</v>
+      <c r="C24" s="41">
+        <f>SUMPRODUCT(C6:C21,E6:E21)/SUM(E6:E21)</f>
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="25" t="inlineStr">
         <is>
-          <t>Cobertura de seguridad (€/MWh)</t>
+          <t>Peajes y ajustes (€/MWh)</t>
         </is>
       </c>
       <c r="B25" s="38" t="n"/>
       <c r="C25" s="42" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="25" t="inlineStr">
         <is>
-          <t>Precio fijo TEÓRICO hoy (€/MWh)</t>
+          <t>Cobertura de seguridad (€/MWh)</t>
         </is>
       </c>
       <c r="B26" s="38" t="n"/>
-      <c r="C26" s="43">
-        <f>C23+C24+C25</f>
-        <v/>
+      <c r="C26" s="42" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="25" t="inlineStr">
         <is>
+          <t>Precio fijo TEÓRICO hoy (€/MWh)</t>
+        </is>
+      </c>
+      <c r="B27" s="38" t="n"/>
+      <c r="C27" s="43">
+        <f>C24+C25+C26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
           <t>Mejor fijo del catálogo — energía (€/MWh)</t>
         </is>
       </c>
-      <c r="B27" s="38" t="n"/>
-      <c r="C27" s="42" t="n">
+      <c r="B28" s="38" t="n"/>
+      <c r="C28" s="42" t="n">
         <v>109.9</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="40" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="40" t="inlineStr">
         <is>
           <t>VENTANA DE FIJACIÓN (teórico − catálogo)</t>
         </is>
       </c>
-      <c r="B28" s="38" t="n"/>
-      <c r="C28" s="41">
-        <f>C26-C27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4">
-        <f>IF(C28&gt;5,"VENTANA ABIERTA: quien fija hoy compra por debajo de donde repreciará el catálogo",IF(C28&lt;-5,"El catálogo está caro frente al mercado: negociar o esperar","Neutral: catálogo alineado con el mercado"))</f>
+      <c r="B29" s="38" t="n"/>
+      <c r="C29" s="41">
+        <f>C27-C28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4">
+        <f>IF(C29&gt;5,"VENTANA ABIERTA: quien fija hoy compra por debajo de donde repreciará el catálogo",IF(C29&lt;-5,"El catálogo está caro frente al mercado: negociar o esperar","Neutral: catálogo alineado con el mercado"))</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A30:E30"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A29:B29"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="A2:H3"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="D4:H4"/>
     <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A22:B22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -1121,15 +1121,15 @@
         <v/>
       </c>
       <c r="I8" s="17">
-        <f>IF($H8="","",IFERROR(VLOOKUP($H8,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H8="","",IFERROR(VLOOKUP($H8,PQ_Diario!$A:$D,2,0),V8))</f>
         <v/>
       </c>
       <c r="J8" s="17">
-        <f>IF($H8="","",IFERROR(VLOOKUP($H8,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H8="","",IFERROR(VLOOKUP($H8,PQ_Diario!$A:$D,3,0),W8))</f>
         <v/>
       </c>
       <c r="K8" s="17">
-        <f>IF($H8="","",IFERROR(VLOOKUP($H8,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H8="","",IFERROR(VLOOKUP($H8,PQ_Diario!$A:$D,4,0),X8))</f>
         <v/>
       </c>
       <c r="Q8" s="18">
@@ -1148,6 +1148,15 @@
       </c>
       <c r="U8" s="19" t="n">
         <v>0.08814</v>
+      </c>
+      <c r="V8" s="20" t="n">
+        <v>63.94</v>
+      </c>
+      <c r="W8" s="20" t="n">
+        <v>166.6</v>
+      </c>
+      <c r="X8" s="20" t="n">
+        <v>238.7</v>
       </c>
     </row>
     <row r="9">
@@ -5912,7 +5921,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -5967,7 +5976,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>138.8</v>
+        <v>143.8</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>1</v>
@@ -5998,7 +6007,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>140</v>
+        <v>143.7</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>1</v>
@@ -6029,7 +6038,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>145.85</v>
+        <v>148.1</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6060,7 +6069,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>125.31</v>
+        <v>127.56</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6091,7 +6100,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>83.5</v>
+        <v>85.75</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6148,7 +6157,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>118</v>
+        <v>120.25</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6174,7 +6183,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>60.75</v>
+        <v>62.2</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6200,7 +6209,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>90.70999999999999</v>
+        <v>93.81999999999999</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6226,7 +6235,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>95.8</v>
+        <v>96</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>1</v>
@@ -6252,7 +6261,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>71.44</v>
+        <v>72.44</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6278,7 +6287,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>44.95</v>
+        <v>45.95</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6330,7 +6339,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>91.25</v>
+        <v>93</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6356,7 +6365,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>60.5</v>
+        <v>61.5</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6382,7 +6391,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>57.65</v>
+        <v>59.35</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -1188,15 +1188,15 @@
         <v/>
       </c>
       <c r="I9" s="17">
-        <f>IF($H9="","",IFERROR(VLOOKUP($H9,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H9="","",IFERROR(VLOOKUP($H9,PQ_Diario!$A:$D,2,0),V9))</f>
         <v/>
       </c>
       <c r="J9" s="17">
-        <f>IF($H9="","",IFERROR(VLOOKUP($H9,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H9="","",IFERROR(VLOOKUP($H9,PQ_Diario!$A:$D,3,0),W9))</f>
         <v/>
       </c>
       <c r="K9" s="17">
-        <f>IF($H9="","",IFERROR(VLOOKUP($H9,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H9="","",IFERROR(VLOOKUP($H9,PQ_Diario!$A:$D,4,0),X9))</f>
         <v/>
       </c>
       <c r="Q9" s="18">
@@ -1215,6 +1215,15 @@
       </c>
       <c r="U9" s="19" t="n">
         <v>0.07088</v>
+      </c>
+      <c r="V9" s="20" t="n">
+        <v>70.69</v>
+      </c>
+      <c r="W9" s="20" t="n">
+        <v>171.85</v>
+      </c>
+      <c r="X9" s="20" t="n">
+        <v>245.07</v>
       </c>
     </row>
     <row r="10">
@@ -5921,7 +5930,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -5976,7 +5985,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>143.8</v>
+        <v>145.1</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>1</v>
@@ -6007,7 +6016,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>143.7</v>
+        <v>144.3</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>1</v>
@@ -6038,7 +6047,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>148.1</v>
+        <v>148</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6069,7 +6078,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>127.56</v>
+        <v>128.85</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6100,7 +6109,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>85.75</v>
+        <v>86.86</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6131,7 +6140,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>47.64</v>
+        <v>48.94</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6157,7 +6166,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>120.25</v>
+        <v>121</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6183,7 +6192,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>62.2</v>
+        <v>63.5</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6209,7 +6218,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>93.81999999999999</v>
+        <v>93.61</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6235,7 +6244,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>96</v>
+        <v>95.78</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>1</v>
@@ -6261,7 +6270,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>72.44</v>
+        <v>73.94</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6287,7 +6296,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>45.95</v>
+        <v>47.45</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6313,7 +6322,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>61.5</v>
+        <v>63</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6339,7 +6348,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>93</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6365,7 +6374,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>61.5</v>
+        <v>63</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6391,7 +6400,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>59.35</v>
+        <v>59</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -5930,7 +5930,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -1255,15 +1255,15 @@
         <v/>
       </c>
       <c r="I10" s="17">
-        <f>IF($H10="","",IFERROR(VLOOKUP($H10,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H10="","",IFERROR(VLOOKUP($H10,PQ_Diario!$A:$D,2,0),V10))</f>
         <v/>
       </c>
       <c r="J10" s="17">
-        <f>IF($H10="","",IFERROR(VLOOKUP($H10,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H10="","",IFERROR(VLOOKUP($H10,PQ_Diario!$A:$D,3,0),W10))</f>
         <v/>
       </c>
       <c r="K10" s="17">
-        <f>IF($H10="","",IFERROR(VLOOKUP($H10,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H10="","",IFERROR(VLOOKUP($H10,PQ_Diario!$A:$D,4,0),X10))</f>
         <v/>
       </c>
       <c r="Q10" s="18">
@@ -1282,6 +1282,15 @@
       </c>
       <c r="U10" s="19" t="n">
         <v>0.07295</v>
+      </c>
+      <c r="V10" s="20" t="n">
+        <v>130</v>
+      </c>
+      <c r="W10" s="20" t="n">
+        <v>196.88</v>
+      </c>
+      <c r="X10" s="20" t="n">
+        <v>271.93</v>
       </c>
     </row>
     <row r="11">
@@ -1313,15 +1322,15 @@
         <v/>
       </c>
       <c r="I11" s="17">
-        <f>IF($H11="","",IFERROR(VLOOKUP($H11,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H11="","",IFERROR(VLOOKUP($H11,PQ_Diario!$A:$D,2,0),V11))</f>
         <v/>
       </c>
       <c r="J11" s="17">
-        <f>IF($H11="","",IFERROR(VLOOKUP($H11,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H11="","",IFERROR(VLOOKUP($H11,PQ_Diario!$A:$D,3,0),W11))</f>
         <v/>
       </c>
       <c r="K11" s="17">
-        <f>IF($H11="","",IFERROR(VLOOKUP($H11,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H11="","",IFERROR(VLOOKUP($H11,PQ_Diario!$A:$D,4,0),X11))</f>
         <v/>
       </c>
       <c r="Q11" s="18">
@@ -1340,6 +1349,15 @@
       </c>
       <c r="U11" s="19" t="n">
         <v>0.08851000000000001</v>
+      </c>
+      <c r="V11" s="20" t="n">
+        <v>147.09</v>
+      </c>
+      <c r="W11" s="20" t="n">
+        <v>201.99</v>
+      </c>
+      <c r="X11" s="20" t="n">
+        <v>281.31</v>
       </c>
     </row>
     <row r="12">
@@ -5930,7 +5948,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46299</v>
+        <v>46301</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -5985,7 +6003,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>145.1</v>
+        <v>145.01</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>1</v>
@@ -6016,7 +6034,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>144.3</v>
+        <v>144.01</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>1</v>
@@ -6047,7 +6065,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>148</v>
+        <v>148.5</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6078,7 +6096,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>128.85</v>
+        <v>127.8</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6109,7 +6127,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>86.86</v>
+        <v>86.01000000000001</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6140,7 +6158,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>48.94</v>
+        <v>48.49</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6166,7 +6184,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>121</v>
+        <v>120.55</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6192,7 +6210,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>63.5</v>
+        <v>63.05</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6218,7 +6236,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>93.61</v>
+        <v>94</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6244,7 +6262,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>95.78</v>
+        <v>98.65000000000001</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>1</v>
@@ -6270,7 +6288,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>73.94</v>
+        <v>73.53</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6296,7 +6314,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>47.45</v>
+        <v>47.19</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6322,7 +6340,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>63</v>
+        <v>62.65</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6348,7 +6366,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>93.40000000000001</v>
+        <v>94</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6374,7 +6392,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>63</v>
+        <v>62.65</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6400,7 +6418,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>59</v>
+        <v>59.25</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -1389,15 +1389,15 @@
         <v/>
       </c>
       <c r="I12" s="17">
-        <f>IF($H12="","",IFERROR(VLOOKUP($H12,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H12="","",IFERROR(VLOOKUP($H12,PQ_Diario!$A:$D,2,0),V12))</f>
         <v/>
       </c>
       <c r="J12" s="17">
-        <f>IF($H12="","",IFERROR(VLOOKUP($H12,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H12="","",IFERROR(VLOOKUP($H12,PQ_Diario!$A:$D,3,0),W12))</f>
         <v/>
       </c>
       <c r="K12" s="17">
-        <f>IF($H12="","",IFERROR(VLOOKUP($H12,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H12="","",IFERROR(VLOOKUP($H12,PQ_Diario!$A:$D,4,0),X12))</f>
         <v/>
       </c>
       <c r="Q12" s="18">
@@ -1416,6 +1416,15 @@
       </c>
       <c r="U12" s="19" t="n">
         <v>0.08432000000000001</v>
+      </c>
+      <c r="V12" s="20" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="W12" s="20" t="n">
+        <v>182.33</v>
+      </c>
+      <c r="X12" s="20" t="n">
+        <v>245.9</v>
       </c>
     </row>
     <row r="13">

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -1456,15 +1456,15 @@
         <v/>
       </c>
       <c r="I13" s="17">
-        <f>IF($H13="","",IFERROR(VLOOKUP($H13,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H13="","",IFERROR(VLOOKUP($H13,PQ_Diario!$A:$D,2,0),V13))</f>
         <v/>
       </c>
       <c r="J13" s="17">
-        <f>IF($H13="","",IFERROR(VLOOKUP($H13,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H13="","",IFERROR(VLOOKUP($H13,PQ_Diario!$A:$D,3,0),W13))</f>
         <v/>
       </c>
       <c r="K13" s="17">
-        <f>IF($H13="","",IFERROR(VLOOKUP($H13,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H13="","",IFERROR(VLOOKUP($H13,PQ_Diario!$A:$D,4,0),X13))</f>
         <v/>
       </c>
       <c r="Q13" s="18">
@@ -1483,6 +1483,15 @@
       </c>
       <c r="U13" s="19" t="n">
         <v>0.09261</v>
+      </c>
+      <c r="V13" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" s="20" t="n">
+        <v>106.9</v>
+      </c>
+      <c r="X13" s="20" t="n">
+        <v>204.5</v>
       </c>
     </row>
     <row r="14">
@@ -5957,7 +5966,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6012,7 +6021,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>145.01</v>
+        <v>147.2</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>1</v>
@@ -6043,7 +6052,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>144.01</v>
+        <v>147.2</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>1</v>
@@ -6074,7 +6083,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>148.5</v>
+        <v>151.2</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6105,7 +6114,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>127.8</v>
+        <v>130.5</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6136,7 +6145,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>86.01000000000001</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6167,7 +6176,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>48.49</v>
+        <v>50.29</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6193,7 +6202,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>120.55</v>
+        <v>123.25</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6219,7 +6228,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>63.05</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6245,7 +6254,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>94</v>
+        <v>96.54000000000001</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6271,7 +6280,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>98.65000000000001</v>
+        <v>102</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>1</v>
@@ -6297,7 +6306,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>73.53</v>
+        <v>74.53</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6323,7 +6332,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>47.19</v>
+        <v>47.83</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6349,7 +6358,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>62.65</v>
+        <v>63.5</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6375,7 +6384,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>94</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6401,7 +6410,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>62.65</v>
+        <v>63.5</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6427,7 +6436,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>59.25</v>
+        <v>60.1</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -1523,15 +1523,15 @@
         <v/>
       </c>
       <c r="I14" s="17">
-        <f>IF($H14="","",IFERROR(VLOOKUP($H14,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H14="","",IFERROR(VLOOKUP($H14,PQ_Diario!$A:$D,2,0),V14))</f>
         <v/>
       </c>
       <c r="J14" s="17">
-        <f>IF($H14="","",IFERROR(VLOOKUP($H14,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H14="","",IFERROR(VLOOKUP($H14,PQ_Diario!$A:$D,3,0),W14))</f>
         <v/>
       </c>
       <c r="K14" s="17">
-        <f>IF($H14="","",IFERROR(VLOOKUP($H14,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H14="","",IFERROR(VLOOKUP($H14,PQ_Diario!$A:$D,4,0),X14))</f>
         <v/>
       </c>
       <c r="Q14" s="18">
@@ -1550,6 +1550,15 @@
       </c>
       <c r="U14" s="19" t="n">
         <v>0.09848</v>
+      </c>
+      <c r="V14" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" s="20" t="n">
+        <v>107.37</v>
+      </c>
+      <c r="X14" s="20" t="n">
+        <v>205</v>
       </c>
     </row>
     <row r="15">
@@ -5966,7 +5975,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6021,7 +6030,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>147.2</v>
+        <v>153</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>1</v>
@@ -6052,7 +6061,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>147.2</v>
+        <v>151.9</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>1</v>
@@ -6083,7 +6092,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>151.2</v>
+        <v>154.5</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6114,7 +6123,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>130.5</v>
+        <v>131.27</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6145,7 +6154,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>88.70999999999999</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6176,7 +6185,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>50.29</v>
+        <v>52.69</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6202,7 +6211,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>123.25</v>
+        <v>125</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6228,7 +6237,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>64.84999999999999</v>
+        <v>67.25</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6254,7 +6263,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>96.54000000000001</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6280,7 +6289,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>1</v>
@@ -6306,7 +6315,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>74.53</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6332,7 +6341,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>47.83</v>
+        <v>48.55</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6358,7 +6367,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>63.5</v>
+        <v>64.45</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6384,7 +6393,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>96.59999999999999</v>
+        <v>97.77</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6410,7 +6419,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>63.5</v>
+        <v>64.45</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6436,7 +6445,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>60.1</v>
+        <v>60.75</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -1590,15 +1590,15 @@
         <v/>
       </c>
       <c r="I15" s="17">
-        <f>IF($H15="","",IFERROR(VLOOKUP($H15,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H15="","",IFERROR(VLOOKUP($H15,PQ_Diario!$A:$D,2,0),V15))</f>
         <v/>
       </c>
       <c r="J15" s="17">
-        <f>IF($H15="","",IFERROR(VLOOKUP($H15,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H15="","",IFERROR(VLOOKUP($H15,PQ_Diario!$A:$D,3,0),W15))</f>
         <v/>
       </c>
       <c r="K15" s="17">
-        <f>IF($H15="","",IFERROR(VLOOKUP($H15,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H15="","",IFERROR(VLOOKUP($H15,PQ_Diario!$A:$D,4,0),X15))</f>
         <v/>
       </c>
       <c r="Q15" s="18">
@@ -1617,6 +1617,15 @@
       </c>
       <c r="U15" s="19" t="n">
         <v>0.08542</v>
+      </c>
+      <c r="V15" s="20" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="W15" s="20" t="n">
+        <v>130</v>
+      </c>
+      <c r="X15" s="20" t="n">
+        <v>219.66</v>
       </c>
     </row>
     <row r="16">
@@ -5975,7 +5984,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6030,7 +6039,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>1</v>
@@ -6061,7 +6070,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>151.9</v>
+        <v>156.5</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>1</v>
@@ -6092,7 +6101,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>154.5</v>
+        <v>159</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6123,7 +6132,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>131.27</v>
+        <v>133.74</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6154,7 +6163,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>89.79000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6185,7 +6194,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>52.69</v>
+        <v>54.94</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6211,7 +6220,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>125</v>
+        <v>128.25</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6237,7 +6246,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>67.25</v>
+        <v>69.5</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6263,7 +6272,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>98.09999999999999</v>
+        <v>100.94</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6289,7 +6298,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>101</v>
+        <v>103.59</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>1</v>
@@ -6315,7 +6324,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>75.65000000000001</v>
+        <v>76.65000000000001</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6341,7 +6350,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>48.55</v>
+        <v>49.19</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6367,7 +6376,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>64.45</v>
+        <v>65.3</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6393,7 +6402,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>97.77</v>
+        <v>100.5</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6419,7 +6428,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>64.45</v>
+        <v>65.3</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6445,7 +6454,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>60.75</v>
+        <v>60.65</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -1657,15 +1657,15 @@
         <v/>
       </c>
       <c r="I16" s="17">
-        <f>IF($H16="","",IFERROR(VLOOKUP($H16,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H16="","",IFERROR(VLOOKUP($H16,PQ_Diario!$A:$D,2,0),V16))</f>
         <v/>
       </c>
       <c r="J16" s="17">
-        <f>IF($H16="","",IFERROR(VLOOKUP($H16,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H16="","",IFERROR(VLOOKUP($H16,PQ_Diario!$A:$D,3,0),W16))</f>
         <v/>
       </c>
       <c r="K16" s="17">
-        <f>IF($H16="","",IFERROR(VLOOKUP($H16,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H16="","",IFERROR(VLOOKUP($H16,PQ_Diario!$A:$D,4,0),X16))</f>
         <v/>
       </c>
       <c r="Q16" s="18">
@@ -1684,6 +1684,15 @@
       </c>
       <c r="U16" s="19" t="n">
         <v>0.05176</v>
+      </c>
+      <c r="V16" s="20" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="W16" s="20" t="n">
+        <v>141.49</v>
+      </c>
+      <c r="X16" s="20" t="n">
+        <v>241.59</v>
       </c>
     </row>
     <row r="17">
@@ -5984,7 +5993,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6039,7 +6048,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>157</v>
+        <v>159.5</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>1</v>
@@ -6070,7 +6079,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>156.5</v>
+        <v>159.3</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>1</v>
@@ -6101,7 +6110,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6132,7 +6141,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>133.74</v>
+        <v>144.72</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6163,7 +6172,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>92.5</v>
+        <v>91.01000000000001</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6194,7 +6203,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>54.94</v>
+        <v>55.69</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6220,7 +6229,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>128.25</v>
+        <v>131.5</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6246,7 +6255,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>69.5</v>
+        <v>70.25</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6272,7 +6281,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>100.94</v>
+        <v>101.28</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6298,7 +6307,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>103.59</v>
+        <v>104.28</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>1</v>
@@ -6402,7 +6411,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>100.5</v>
+        <v>101.75</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6454,7 +6463,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>60.65</v>
+        <v>62.5</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -1724,15 +1724,15 @@
         <v/>
       </c>
       <c r="I17" s="17">
-        <f>IF($H17="","",IFERROR(VLOOKUP($H17,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H17="","",IFERROR(VLOOKUP($H17,PQ_Diario!$A:$D,2,0),V17))</f>
         <v/>
       </c>
       <c r="J17" s="17">
-        <f>IF($H17="","",IFERROR(VLOOKUP($H17,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H17="","",IFERROR(VLOOKUP($H17,PQ_Diario!$A:$D,3,0),W17))</f>
         <v/>
       </c>
       <c r="K17" s="17">
-        <f>IF($H17="","",IFERROR(VLOOKUP($H17,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H17="","",IFERROR(VLOOKUP($H17,PQ_Diario!$A:$D,4,0),X17))</f>
         <v/>
       </c>
       <c r="Q17" s="18">
@@ -1751,6 +1751,15 @@
       </c>
       <c r="U17" s="19" t="n">
         <v>0.06365</v>
+      </c>
+      <c r="V17" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" s="20" t="n">
+        <v>151.76</v>
+      </c>
+      <c r="X17" s="20" t="n">
+        <v>273.01</v>
       </c>
     </row>
     <row r="18">
@@ -5993,7 +6002,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -1791,15 +1791,15 @@
         <v/>
       </c>
       <c r="I18" s="17">
-        <f>IF($H18="","",IFERROR(VLOOKUP($H18,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H18="","",IFERROR(VLOOKUP($H18,PQ_Diario!$A:$D,2,0),V18))</f>
         <v/>
       </c>
       <c r="J18" s="17">
-        <f>IF($H18="","",IFERROR(VLOOKUP($H18,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H18="","",IFERROR(VLOOKUP($H18,PQ_Diario!$A:$D,3,0),W18))</f>
         <v/>
       </c>
       <c r="K18" s="17">
-        <f>IF($H18="","",IFERROR(VLOOKUP($H18,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H18="","",IFERROR(VLOOKUP($H18,PQ_Diario!$A:$D,4,0),X18))</f>
         <v/>
       </c>
       <c r="Q18" s="21">
@@ -1818,6 +1818,15 @@
       </c>
       <c r="U18" s="19" t="n">
         <v>0.06423</v>
+      </c>
+      <c r="V18" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="W18" s="20" t="n">
+        <v>166.63</v>
+      </c>
+      <c r="X18" s="20" t="n">
+        <v>269.29</v>
       </c>
     </row>
     <row r="19">
@@ -6002,7 +6011,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46306</v>
+        <v>46308</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6057,7 +6066,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>159.5</v>
+        <v>163.6</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>1</v>
@@ -6088,7 +6097,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>159.3</v>
+        <v>163.6</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>1</v>
@@ -6119,7 +6128,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6150,7 +6159,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>144.72</v>
+        <v>149.54</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6181,7 +6190,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>91.01000000000001</v>
+        <v>95.72</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6212,7 +6221,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>55.69</v>
+        <v>56.44</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6238,7 +6247,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>131.5</v>
+        <v>136</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6264,7 +6273,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>70.25</v>
+        <v>71</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6290,7 +6299,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>101.28</v>
+        <v>102.17</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6316,7 +6325,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>104.28</v>
+        <v>105.2</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>1</v>
@@ -6342,7 +6351,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>76.65000000000001</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6368,7 +6377,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>49.19</v>
+        <v>50.28</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6394,7 +6403,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>65.3</v>
+        <v>66.75</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6420,7 +6429,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>101.75</v>
+        <v>103.5</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6446,7 +6455,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>65.3</v>
+        <v>66.75</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -1858,15 +1858,15 @@
         <v/>
       </c>
       <c r="I19" s="17">
-        <f>IF($H19="","",IFERROR(VLOOKUP($H19,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H19="","",IFERROR(VLOOKUP($H19,PQ_Diario!$A:$D,2,0),V19))</f>
         <v/>
       </c>
       <c r="J19" s="17">
-        <f>IF($H19="","",IFERROR(VLOOKUP($H19,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H19="","",IFERROR(VLOOKUP($H19,PQ_Diario!$A:$D,3,0),W19))</f>
         <v/>
       </c>
       <c r="K19" s="17">
-        <f>IF($H19="","",IFERROR(VLOOKUP($H19,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H19="","",IFERROR(VLOOKUP($H19,PQ_Diario!$A:$D,4,0),X19))</f>
         <v/>
       </c>
       <c r="S19" s="19" t="n">
@@ -1877,6 +1877,15 @@
       </c>
       <c r="U19" s="19" t="n">
         <v>0.03621</v>
+      </c>
+      <c r="V19" s="20" t="n">
+        <v>57.66</v>
+      </c>
+      <c r="W19" s="20" t="n">
+        <v>186.44</v>
+      </c>
+      <c r="X19" s="20" t="n">
+        <v>299</v>
       </c>
     </row>
     <row r="20">

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -1882,7 +1882,7 @@
         <v>57.66</v>
       </c>
       <c r="W19" s="20" t="n">
-        <v>186.44</v>
+        <v>186.45</v>
       </c>
       <c r="X19" s="20" t="n">
         <v>299</v>
@@ -1917,15 +1917,15 @@
         <v/>
       </c>
       <c r="I20" s="17">
-        <f>IF($H20="","",IFERROR(VLOOKUP($H20,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H20="","",IFERROR(VLOOKUP($H20,PQ_Diario!$A:$D,2,0),V20))</f>
         <v/>
       </c>
       <c r="J20" s="17">
-        <f>IF($H20="","",IFERROR(VLOOKUP($H20,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H20="","",IFERROR(VLOOKUP($H20,PQ_Diario!$A:$D,3,0),W20))</f>
         <v/>
       </c>
       <c r="K20" s="17">
-        <f>IF($H20="","",IFERROR(VLOOKUP($H20,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H20="","",IFERROR(VLOOKUP($H20,PQ_Diario!$A:$D,4,0),X20))</f>
         <v/>
       </c>
       <c r="S20" s="19" t="n">
@@ -1936,6 +1936,15 @@
       </c>
       <c r="U20" s="19" t="n">
         <v>0.01494</v>
+      </c>
+      <c r="V20" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="W20" s="20" t="n">
+        <v>193.11</v>
+      </c>
+      <c r="X20" s="20" t="n">
+        <v>297.5</v>
       </c>
     </row>
     <row r="21">
@@ -6020,7 +6029,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6075,7 +6084,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>163.6</v>
+        <v>168</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>1</v>
@@ -6106,7 +6115,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>163.6</v>
+        <v>169.5</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>1</v>
@@ -6137,7 +6146,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>164</v>
+        <v>168.7</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6168,7 +6177,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>149.54</v>
+        <v>154.73</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6199,7 +6208,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>95.72</v>
+        <v>100.84</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6230,7 +6239,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>56.44</v>
+        <v>59.09</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6256,7 +6265,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6282,7 +6291,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>71</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6308,7 +6317,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>102.17</v>
+        <v>105.4</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6334,7 +6343,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>105.2</v>
+        <v>107.55</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>1</v>
@@ -6360,7 +6369,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>78.34999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6386,7 +6395,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>50.28</v>
+        <v>50.13</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6412,7 +6421,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>66.75</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6438,7 +6447,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>103.5</v>
+        <v>106.8</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6464,7 +6473,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>66.75</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6490,7 +6499,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>62.5</v>
+        <v>63.25</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -1976,15 +1976,15 @@
         <v/>
       </c>
       <c r="I21" s="17">
-        <f>IF($H21="","",IFERROR(VLOOKUP($H21,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H21="","",IFERROR(VLOOKUP($H21,PQ_Diario!$A:$D,2,0),V21))</f>
         <v/>
       </c>
       <c r="J21" s="17">
-        <f>IF($H21="","",IFERROR(VLOOKUP($H21,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H21="","",IFERROR(VLOOKUP($H21,PQ_Diario!$A:$D,3,0),W21))</f>
         <v/>
       </c>
       <c r="K21" s="17">
-        <f>IF($H21="","",IFERROR(VLOOKUP($H21,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H21="","",IFERROR(VLOOKUP($H21,PQ_Diario!$A:$D,4,0),X21))</f>
         <v/>
       </c>
       <c r="S21" s="19" t="n">
@@ -1995,6 +1995,15 @@
       </c>
       <c r="U21" s="19" t="n">
         <v>0.01337</v>
+      </c>
+      <c r="V21" s="20" t="n">
+        <v>79.26000000000001</v>
+      </c>
+      <c r="W21" s="20" t="n">
+        <v>191.64</v>
+      </c>
+      <c r="X21" s="20" t="n">
+        <v>285.95</v>
       </c>
     </row>
     <row r="22">
@@ -6029,7 +6038,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6084,7 +6093,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>168</v>
+        <v>164.75</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>1</v>
@@ -6115,7 +6124,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>169.5</v>
+        <v>167.42</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>1</v>
@@ -6146,7 +6155,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>168.7</v>
+        <v>167.29</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6177,7 +6186,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>154.73</v>
+        <v>154</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6208,7 +6217,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>100.84</v>
+        <v>100.01</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6239,7 +6248,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>59.09</v>
+        <v>60.44</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6265,7 +6274,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6291,7 +6300,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>73.65000000000001</v>
+        <v>75</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6317,7 +6326,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>105.4</v>
+        <v>106.75</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6343,7 +6352,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>107.55</v>
+        <v>109.61</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>1</v>
@@ -6369,7 +6378,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>78.2</v>
+        <v>78.84999999999999</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6395,7 +6404,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>50.13</v>
+        <v>50.78</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6421,7 +6430,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>66.59999999999999</v>
+        <v>67.25</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6447,7 +6456,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>106.8</v>
+        <v>107.75</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6473,7 +6482,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>66.59999999999999</v>
+        <v>67.25</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6499,7 +6508,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>63.25</v>
+        <v>63.75</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -2035,15 +2035,15 @@
         <v/>
       </c>
       <c r="I22" s="17">
-        <f>IF($H22="","",IFERROR(VLOOKUP($H22,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H22="","",IFERROR(VLOOKUP($H22,PQ_Diario!$A:$D,2,0),V22))</f>
         <v/>
       </c>
       <c r="J22" s="17">
-        <f>IF($H22="","",IFERROR(VLOOKUP($H22,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H22="","",IFERROR(VLOOKUP($H22,PQ_Diario!$A:$D,3,0),W22))</f>
         <v/>
       </c>
       <c r="K22" s="17">
-        <f>IF($H22="","",IFERROR(VLOOKUP($H22,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H22="","",IFERROR(VLOOKUP($H22,PQ_Diario!$A:$D,4,0),X22))</f>
         <v/>
       </c>
       <c r="S22" s="19" t="n">
@@ -2054,6 +2054,15 @@
       </c>
       <c r="U22" s="19" t="n">
         <v>0.03306</v>
+      </c>
+      <c r="V22" s="20" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="W22" s="20" t="n">
+        <v>107.15</v>
+      </c>
+      <c r="X22" s="20" t="n">
+        <v>212.04</v>
       </c>
     </row>
     <row r="23">
@@ -6038,7 +6047,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6093,7 +6102,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>164.75</v>
+        <v>165</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>1</v>
@@ -6124,7 +6133,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>167.42</v>
+        <v>167.5</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>1</v>
@@ -6155,7 +6164,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>167.29</v>
+        <v>168</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6186,7 +6195,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>154</v>
+        <v>154.29</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6217,7 +6226,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>100.01</v>
+        <v>100.2</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6248,7 +6257,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>60.44</v>
+        <v>62.19</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6274,7 +6283,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>140</v>
+        <v>140.4</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6300,7 +6309,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>75</v>
+        <v>76.75</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6326,7 +6335,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>106.75</v>
+        <v>108.7</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6352,7 +6361,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>109.61</v>
+        <v>109.5</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>1</v>
@@ -6378,7 +6387,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>78.84999999999999</v>
+        <v>79.34999999999999</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6404,7 +6413,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>50.78</v>
+        <v>51.28</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6430,7 +6439,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>67.25</v>
+        <v>67.75</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6456,7 +6465,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>107.75</v>
+        <v>108.75</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6482,7 +6491,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>67.25</v>
+        <v>67.75</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6508,7 +6517,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>63.75</v>
+        <v>63</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -2094,15 +2094,15 @@
         <v/>
       </c>
       <c r="I23" s="17">
-        <f>IF($H23="","",IFERROR(VLOOKUP($H23,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H23="","",IFERROR(VLOOKUP($H23,PQ_Diario!$A:$D,2,0),V23))</f>
         <v/>
       </c>
       <c r="J23" s="17">
-        <f>IF($H23="","",IFERROR(VLOOKUP($H23,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H23="","",IFERROR(VLOOKUP($H23,PQ_Diario!$A:$D,3,0),W23))</f>
         <v/>
       </c>
       <c r="K23" s="17">
-        <f>IF($H23="","",IFERROR(VLOOKUP($H23,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H23="","",IFERROR(VLOOKUP($H23,PQ_Diario!$A:$D,4,0),X23))</f>
         <v/>
       </c>
       <c r="S23" s="19" t="n">
@@ -2113,6 +2113,15 @@
       </c>
       <c r="U23" s="19" t="n">
         <v>0.05189</v>
+      </c>
+      <c r="V23" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" s="20" t="n">
+        <v>76.28</v>
+      </c>
+      <c r="X23" s="20" t="n">
+        <v>185.8</v>
       </c>
     </row>
     <row r="24">
@@ -6047,7 +6056,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6102,7 +6111,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>165</v>
+        <v>165.5</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>1</v>
@@ -6133,7 +6142,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>167.5</v>
+        <v>168</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>1</v>
@@ -6164,7 +6173,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>168</v>
+        <v>169.65</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6195,7 +6204,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>154.29</v>
+        <v>159.29</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6226,7 +6235,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>100.2</v>
+        <v>97.51000000000001</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6257,7 +6266,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>62.19</v>
+        <v>64.44</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6283,7 +6292,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>140.4</v>
+        <v>141.6</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6309,7 +6318,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>76.75</v>
+        <v>79</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6335,7 +6344,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>108.7</v>
+        <v>112.8</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6361,7 +6370,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>109.5</v>
+        <v>113.31</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>1</v>
@@ -6387,7 +6396,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>79.34999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6413,7 +6422,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>51.28</v>
+        <v>52.42</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6439,7 +6448,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>67.75</v>
+        <v>69.25</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6465,7 +6474,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>108.75</v>
+        <v>111.6</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6491,7 +6500,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>67.75</v>
+        <v>69.25</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6517,7 +6526,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>63</v>
+        <v>64.3</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -2153,15 +2153,15 @@
         <v/>
       </c>
       <c r="I24" s="17">
-        <f>IF($H24="","",IFERROR(VLOOKUP($H24,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H24="","",IFERROR(VLOOKUP($H24,PQ_Diario!$A:$D,2,0),V24))</f>
         <v/>
       </c>
       <c r="J24" s="17">
-        <f>IF($H24="","",IFERROR(VLOOKUP($H24,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H24="","",IFERROR(VLOOKUP($H24,PQ_Diario!$A:$D,3,0),W24))</f>
         <v/>
       </c>
       <c r="K24" s="17">
-        <f>IF($H24="","",IFERROR(VLOOKUP($H24,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H24="","",IFERROR(VLOOKUP($H24,PQ_Diario!$A:$D,4,0),X24))</f>
         <v/>
       </c>
       <c r="S24" s="19" t="n">
@@ -2172,6 +2172,15 @@
       </c>
       <c r="U24" s="19" t="n">
         <v>0.07045</v>
+      </c>
+      <c r="V24" s="20" t="n">
+        <v>168.5</v>
+      </c>
+      <c r="W24" s="20" t="n">
+        <v>215.11</v>
+      </c>
+      <c r="X24" s="20" t="n">
+        <v>299</v>
       </c>
     </row>
     <row r="25">
@@ -6056,7 +6065,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -2212,15 +2212,15 @@
         <v/>
       </c>
       <c r="I25" s="17">
-        <f>IF($H25="","",IFERROR(VLOOKUP($H25,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H25="","",IFERROR(VLOOKUP($H25,PQ_Diario!$A:$D,2,0),V25))</f>
         <v/>
       </c>
       <c r="J25" s="17">
-        <f>IF($H25="","",IFERROR(VLOOKUP($H25,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H25="","",IFERROR(VLOOKUP($H25,PQ_Diario!$A:$D,3,0),W25))</f>
         <v/>
       </c>
       <c r="K25" s="17">
-        <f>IF($H25="","",IFERROR(VLOOKUP($H25,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H25="","",IFERROR(VLOOKUP($H25,PQ_Diario!$A:$D,4,0),X25))</f>
         <v/>
       </c>
       <c r="S25" s="19" t="n">
@@ -2231,6 +2231,15 @@
       </c>
       <c r="U25" s="19" t="n">
         <v>0.08558</v>
+      </c>
+      <c r="V25" s="20" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="W25" s="20" t="n">
+        <v>195.52</v>
+      </c>
+      <c r="X25" s="20" t="n">
+        <v>278.87</v>
       </c>
     </row>
     <row r="26">
@@ -6065,7 +6074,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -2271,15 +2271,15 @@
         <v/>
       </c>
       <c r="I26" s="17">
-        <f>IF($H26="","",IFERROR(VLOOKUP($H26,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H26="","",IFERROR(VLOOKUP($H26,PQ_Diario!$A:$D,2,0),V26))</f>
         <v/>
       </c>
       <c r="J26" s="17">
-        <f>IF($H26="","",IFERROR(VLOOKUP($H26,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H26="","",IFERROR(VLOOKUP($H26,PQ_Diario!$A:$D,3,0),W26))</f>
         <v/>
       </c>
       <c r="K26" s="17">
-        <f>IF($H26="","",IFERROR(VLOOKUP($H26,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H26="","",IFERROR(VLOOKUP($H26,PQ_Diario!$A:$D,4,0),X26))</f>
         <v/>
       </c>
       <c r="S26" s="19" t="n">
@@ -2290,6 +2290,15 @@
       </c>
       <c r="U26" s="19" t="n">
         <v>0.0725</v>
+      </c>
+      <c r="V26" s="20" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W26" s="20" t="n">
+        <v>146.97</v>
+      </c>
+      <c r="X26" s="20" t="n">
+        <v>299</v>
       </c>
     </row>
     <row r="27">
@@ -6074,7 +6083,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6129,7 +6138,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>165.5</v>
+        <v>168.5</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>1</v>
@@ -6160,7 +6169,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>168</v>
+        <v>170.25</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>1</v>
@@ -6191,7 +6200,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>169.65</v>
+        <v>172.77</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6222,7 +6231,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>159.29</v>
+        <v>165</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6253,7 +6262,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>97.51000000000001</v>
+        <v>102.01</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6284,7 +6293,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>64.44</v>
+        <v>75</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6310,7 +6319,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>141.6</v>
+        <v>146</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6336,7 +6345,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>79</v>
+        <v>85.75</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6362,7 +6371,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>112.8</v>
+        <v>117</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6388,7 +6397,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>113.31</v>
+        <v>114.99</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>1</v>
@@ -6414,7 +6423,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>79.5</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6440,7 +6449,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>52.42</v>
+        <v>53.74</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6466,7 +6475,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>69.25</v>
+        <v>71</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6492,7 +6501,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>111.6</v>
+        <v>115.85</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6518,7 +6527,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>69.25</v>
+        <v>71</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6544,7 +6553,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>64.3</v>
+        <v>65.25</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -2330,15 +2330,15 @@
         <v/>
       </c>
       <c r="I27" s="17">
-        <f>IF($H27="","",IFERROR(VLOOKUP($H27,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H27="","",IFERROR(VLOOKUP($H27,PQ_Diario!$A:$D,2,0),V27))</f>
         <v/>
       </c>
       <c r="J27" s="17">
-        <f>IF($H27="","",IFERROR(VLOOKUP($H27,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H27="","",IFERROR(VLOOKUP($H27,PQ_Diario!$A:$D,3,0),W27))</f>
         <v/>
       </c>
       <c r="K27" s="17">
-        <f>IF($H27="","",IFERROR(VLOOKUP($H27,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H27="","",IFERROR(VLOOKUP($H27,PQ_Diario!$A:$D,4,0),X27))</f>
         <v/>
       </c>
       <c r="S27" s="19" t="n">
@@ -2349,6 +2349,15 @@
       </c>
       <c r="U27" s="19" t="n">
         <v>0.0595</v>
+      </c>
+      <c r="V27" s="20" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="W27" s="20" t="n">
+        <v>155.63</v>
+      </c>
+      <c r="X27" s="20" t="n">
+        <v>286.76</v>
       </c>
     </row>
     <row r="28">
@@ -6083,7 +6092,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6138,7 +6147,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>168.5</v>
+        <v>165.5</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>1</v>
@@ -6169,7 +6178,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>170.25</v>
+        <v>168</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>1</v>
@@ -6200,7 +6209,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>172.77</v>
+        <v>168.96</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6231,7 +6240,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>165</v>
+        <v>158.31</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6262,7 +6271,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>102.01</v>
+        <v>97.48999999999999</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6293,7 +6302,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>75</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6319,7 +6328,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>146</v>
+        <v>141.05</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6345,7 +6354,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>85.75</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6371,7 +6380,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>117</v>
+        <v>114.65</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6397,7 +6406,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>114.99</v>
+        <v>114.5</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>1</v>
@@ -6423,7 +6432,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>81.51000000000001</v>
+        <v>80.36</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6449,7 +6458,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>53.74</v>
+        <v>52.98</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6475,7 +6484,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6501,7 +6510,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>115.85</v>
+        <v>113.14</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6527,7 +6536,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -2389,15 +2389,15 @@
         <v/>
       </c>
       <c r="I28" s="17">
-        <f>IF($H28="","",IFERROR(VLOOKUP($H28,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H28="","",IFERROR(VLOOKUP($H28,PQ_Diario!$A:$D,2,0),V28))</f>
         <v/>
       </c>
       <c r="J28" s="17">
-        <f>IF($H28="","",IFERROR(VLOOKUP($H28,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H28="","",IFERROR(VLOOKUP($H28,PQ_Diario!$A:$D,3,0),W28))</f>
         <v/>
       </c>
       <c r="K28" s="17">
-        <f>IF($H28="","",IFERROR(VLOOKUP($H28,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H28="","",IFERROR(VLOOKUP($H28,PQ_Diario!$A:$D,4,0),X28))</f>
         <v/>
       </c>
       <c r="S28" s="19" t="n">
@@ -2408,6 +2408,15 @@
       </c>
       <c r="U28" s="19" t="n">
         <v>0.09408999999999999</v>
+      </c>
+      <c r="V28" s="20" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="W28" s="20" t="n">
+        <v>110.09</v>
+      </c>
+      <c r="X28" s="20" t="n">
+        <v>224</v>
       </c>
     </row>
     <row r="29">
@@ -6092,7 +6101,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6147,7 +6156,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>165.5</v>
+        <v>171.5</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>1</v>
@@ -6178,7 +6187,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>168</v>
+        <v>174.5</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>1</v>
@@ -6209,7 +6218,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>168.96</v>
+        <v>175.91</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6240,7 +6249,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>158.31</v>
+        <v>165.26</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6271,7 +6280,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>97.48999999999999</v>
+        <v>104.44</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6302,7 +6311,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>71.90000000000001</v>
+        <v>73</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6328,7 +6337,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>141.05</v>
+        <v>148</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6354,7 +6363,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>82.65000000000001</v>
+        <v>83.75</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6380,7 +6389,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>114.65</v>
+        <v>117</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6406,7 +6415,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>114.5</v>
+        <v>116.5</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>1</v>
@@ -6432,7 +6441,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>80.36</v>
+        <v>80</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6458,7 +6467,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>52.98</v>
+        <v>52.75</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6484,7 +6493,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>70</v>
+        <v>69.7</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6510,7 +6519,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>113.14</v>
+        <v>116.22</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6536,7 +6545,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>70</v>
+        <v>69.7</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6562,7 +6571,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>65.25</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -2448,15 +2448,15 @@
         <v/>
       </c>
       <c r="I29" s="17">
-        <f>IF($H29="","",IFERROR(VLOOKUP($H29,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H29="","",IFERROR(VLOOKUP($H29,PQ_Diario!$A:$D,2,0),V29))</f>
         <v/>
       </c>
       <c r="J29" s="17">
-        <f>IF($H29="","",IFERROR(VLOOKUP($H29,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H29="","",IFERROR(VLOOKUP($H29,PQ_Diario!$A:$D,3,0),W29))</f>
         <v/>
       </c>
       <c r="K29" s="17">
-        <f>IF($H29="","",IFERROR(VLOOKUP($H29,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H29="","",IFERROR(VLOOKUP($H29,PQ_Diario!$A:$D,4,0),X29))</f>
         <v/>
       </c>
       <c r="S29" s="19" t="n">
@@ -2467,6 +2467,15 @@
       </c>
       <c r="U29" s="19" t="n">
         <v>0.10005</v>
+      </c>
+      <c r="V29" s="20" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="W29" s="20" t="n">
+        <v>137.19</v>
+      </c>
+      <c r="X29" s="20" t="n">
+        <v>226</v>
       </c>
     </row>
     <row r="30">
@@ -6101,7 +6110,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6156,7 +6165,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>171.5</v>
+        <v>179.5</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>1</v>
@@ -6187,7 +6196,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>174.5</v>
+        <v>181.4</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>1</v>
@@ -6218,7 +6227,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>175.91</v>
+        <v>184.95</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6249,7 +6258,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>165.26</v>
+        <v>171.31</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6280,7 +6289,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>104.44</v>
+        <v>106.63</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6311,7 +6320,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>73</v>
+        <v>78.95</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6337,7 +6346,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>148</v>
+        <v>153.75</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6363,7 +6372,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>83.75</v>
+        <v>86.73999999999999</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6389,7 +6398,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>117</v>
+        <v>122.06</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6415,7 +6424,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>116.5</v>
+        <v>119.82</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>1</v>
@@ -6441,7 +6450,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>80</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6467,7 +6476,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>52.75</v>
+        <v>53.85</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6493,7 +6502,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>69.7</v>
+        <v>70.8</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6519,7 +6528,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>116.22</v>
+        <v>120.5</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6545,7 +6554,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>69.7</v>
+        <v>70.8</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6571,7 +6580,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>65.34999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -2507,15 +2507,15 @@
         <v/>
       </c>
       <c r="I30" s="17">
-        <f>IF($H30="","",IFERROR(VLOOKUP($H30,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H30="","",IFERROR(VLOOKUP($H30,PQ_Diario!$A:$D,2,0),V30))</f>
         <v/>
       </c>
       <c r="J30" s="17">
-        <f>IF($H30="","",IFERROR(VLOOKUP($H30,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H30="","",IFERROR(VLOOKUP($H30,PQ_Diario!$A:$D,3,0),W30))</f>
         <v/>
       </c>
       <c r="K30" s="17">
-        <f>IF($H30="","",IFERROR(VLOOKUP($H30,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H30="","",IFERROR(VLOOKUP($H30,PQ_Diario!$A:$D,4,0),X30))</f>
         <v/>
       </c>
       <c r="S30" s="19" t="n">
@@ -2526,6 +2526,15 @@
       </c>
       <c r="U30" s="19" t="n">
         <v>0.08304</v>
+      </c>
+      <c r="V30" s="20" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="W30" s="20" t="n">
+        <v>111.88</v>
+      </c>
+      <c r="X30" s="20" t="n">
+        <v>250.59</v>
       </c>
     </row>
     <row r="31">
@@ -6110,7 +6119,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6165,7 +6174,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>179.5</v>
+        <v>186.5</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>1</v>
@@ -6196,7 +6205,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>181.4</v>
+        <v>189</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>1</v>
@@ -6227,7 +6236,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>184.95</v>
+        <v>195</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6258,7 +6267,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>171.31</v>
+        <v>184.22</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6289,7 +6298,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>106.63</v>
+        <v>114.67</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6320,7 +6329,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>78.95</v>
+        <v>84.69</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6346,7 +6355,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>153.75</v>
+        <v>164</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6372,7 +6381,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>86.73999999999999</v>
+        <v>93.05</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6398,7 +6407,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>122.06</v>
+        <v>129.11</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6424,7 +6433,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>119.82</v>
+        <v>126.86</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>1</v>
@@ -6450,7 +6459,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>81.09999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6476,7 +6485,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>53.85</v>
+        <v>56.05</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6502,7 +6511,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>70.8</v>
+        <v>73</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6528,7 +6537,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>120.5</v>
+        <v>128.15</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6554,7 +6563,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>70.8</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6580,7 +6589,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>66.2</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -2531,7 +2531,7 @@
         <v>-1.46</v>
       </c>
       <c r="W30" s="20" t="n">
-        <v>111.88</v>
+        <v>106.94</v>
       </c>
       <c r="X30" s="20" t="n">
         <v>250.59</v>
@@ -2566,15 +2566,15 @@
         <v/>
       </c>
       <c r="I31" s="17">
-        <f>IF($H31="","",IFERROR(VLOOKUP($H31,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H31="","",IFERROR(VLOOKUP($H31,PQ_Diario!$A:$D,2,0),V31))</f>
         <v/>
       </c>
       <c r="J31" s="17">
-        <f>IF($H31="","",IFERROR(VLOOKUP($H31,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H31="","",IFERROR(VLOOKUP($H31,PQ_Diario!$A:$D,3,0),W31))</f>
         <v/>
       </c>
       <c r="K31" s="17">
-        <f>IF($H31="","",IFERROR(VLOOKUP($H31,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H31="","",IFERROR(VLOOKUP($H31,PQ_Diario!$A:$D,4,0),X31))</f>
         <v/>
       </c>
       <c r="S31" s="19" t="n">
@@ -2585,6 +2585,15 @@
       </c>
       <c r="U31" s="19" t="n">
         <v>0.10093</v>
+      </c>
+      <c r="V31" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="W31" s="20" t="n">
+        <v>196.86</v>
+      </c>
+      <c r="X31" s="20" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="32">
@@ -6119,7 +6128,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -2625,15 +2625,15 @@
         <v/>
       </c>
       <c r="I32" s="17">
-        <f>IF($H32="","",IFERROR(VLOOKUP($H32,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H32="","",IFERROR(VLOOKUP($H32,PQ_Diario!$A:$D,2,0),V32))</f>
         <v/>
       </c>
       <c r="J32" s="17">
-        <f>IF($H32="","",IFERROR(VLOOKUP($H32,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H32="","",IFERROR(VLOOKUP($H32,PQ_Diario!$A:$D,3,0),W32))</f>
         <v/>
       </c>
       <c r="K32" s="17">
-        <f>IF($H32="","",IFERROR(VLOOKUP($H32,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H32="","",IFERROR(VLOOKUP($H32,PQ_Diario!$A:$D,4,0),X32))</f>
         <v/>
       </c>
       <c r="S32" s="19" t="n">
@@ -2644,6 +2644,15 @@
       </c>
       <c r="U32" s="19" t="n">
         <v>0.04494</v>
+      </c>
+      <c r="V32" s="20" t="n">
+        <v>100</v>
+      </c>
+      <c r="W32" s="20" t="n">
+        <v>206.89</v>
+      </c>
+      <c r="X32" s="20" t="n">
+        <v>290</v>
       </c>
     </row>
     <row r="33">
@@ -6128,7 +6137,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -2684,15 +2684,15 @@
         <v/>
       </c>
       <c r="I33" s="17">
-        <f>IF($H33="","",IFERROR(VLOOKUP($H33,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H33="","",IFERROR(VLOOKUP($H33,PQ_Diario!$A:$D,2,0),V33))</f>
         <v/>
       </c>
       <c r="J33" s="17">
-        <f>IF($H33="","",IFERROR(VLOOKUP($H33,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H33="","",IFERROR(VLOOKUP($H33,PQ_Diario!$A:$D,3,0),W33))</f>
         <v/>
       </c>
       <c r="K33" s="17">
-        <f>IF($H33="","",IFERROR(VLOOKUP($H33,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H33="","",IFERROR(VLOOKUP($H33,PQ_Diario!$A:$D,4,0),X33))</f>
         <v/>
       </c>
       <c r="S33" s="19" t="n">
@@ -2703,6 +2703,15 @@
       </c>
       <c r="U33" s="19" t="n">
         <v>0.02598</v>
+      </c>
+      <c r="V33" s="20" t="n">
+        <v>57.08</v>
+      </c>
+      <c r="W33" s="20" t="n">
+        <v>197.46</v>
+      </c>
+      <c r="X33" s="20" t="n">
+        <v>319</v>
       </c>
     </row>
     <row r="34">
@@ -6137,7 +6146,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6192,7 +6201,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>186.5</v>
+        <v>201</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>1</v>
@@ -6223,7 +6232,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>1</v>
@@ -6254,7 +6263,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>195</v>
+        <v>203.5</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6285,7 +6294,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>184.22</v>
+        <v>193.07</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6316,7 +6325,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>114.67</v>
+        <v>119.95</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6347,7 +6356,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>84.69</v>
+        <v>90</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6373,7 +6382,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>164</v>
+        <v>171.5</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6399,7 +6408,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>93.05</v>
+        <v>97.25</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6425,7 +6434,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>129.11</v>
+        <v>135.68</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6451,7 +6460,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>126.86</v>
+        <v>133</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>1</v>
@@ -6477,7 +6486,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>82.5</v>
+        <v>85.28</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6503,7 +6512,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>56.05</v>
+        <v>58.83</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6529,7 +6538,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>73</v>
+        <v>75.45999999999999</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6555,7 +6564,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>128.15</v>
+        <v>134.25</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6581,7 +6590,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>71.34999999999999</v>
+        <v>73.75</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6607,7 +6616,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>65.48999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -2743,15 +2743,15 @@
         <v/>
       </c>
       <c r="I34" s="17">
-        <f>IF($H34="","",IFERROR(VLOOKUP($H34,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H34="","",IFERROR(VLOOKUP($H34,PQ_Diario!$A:$D,2,0),V34))</f>
         <v/>
       </c>
       <c r="J34" s="17">
-        <f>IF($H34="","",IFERROR(VLOOKUP($H34,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H34="","",IFERROR(VLOOKUP($H34,PQ_Diario!$A:$D,3,0),W34))</f>
         <v/>
       </c>
       <c r="K34" s="17">
-        <f>IF($H34="","",IFERROR(VLOOKUP($H34,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H34="","",IFERROR(VLOOKUP($H34,PQ_Diario!$A:$D,4,0),X34))</f>
         <v/>
       </c>
       <c r="S34" s="19" t="n">
@@ -2762,6 +2762,15 @@
       </c>
       <c r="U34" s="19" t="n">
         <v>0.01711</v>
+      </c>
+      <c r="V34" s="20" t="n">
+        <v>115</v>
+      </c>
+      <c r="W34" s="20" t="n">
+        <v>231.01</v>
+      </c>
+      <c r="X34" s="20" t="n">
+        <v>322.78</v>
       </c>
     </row>
     <row r="35">
@@ -6146,7 +6155,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6201,7 +6210,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>201</v>
+        <v>192.7</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>1</v>
@@ -6232,7 +6241,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>197</v>
+        <v>193.25</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>1</v>
@@ -6263,7 +6272,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>203.5</v>
+        <v>197.53</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6294,7 +6303,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>193.07</v>
+        <v>188.68</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6325,7 +6334,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>119.95</v>
+        <v>118.42</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6356,7 +6365,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>90</v>
+        <v>86.98999999999999</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6382,7 +6391,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>171.5</v>
+        <v>167.55</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6408,7 +6417,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>97.25</v>
+        <v>94</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6434,7 +6443,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>135.68</v>
+        <v>128.91</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6460,7 +6469,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>1</v>
@@ -6486,7 +6495,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>85.28</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6512,7 +6521,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>58.83</v>
+        <v>58.88</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6538,7 +6547,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>75.45999999999999</v>
+        <v>73</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6564,7 +6573,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>134.25</v>
+        <v>129.5</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6590,7 +6599,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>73.75</v>
+        <v>73.8</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6616,7 +6625,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>67.5</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -2802,15 +2802,15 @@
         <v/>
       </c>
       <c r="I35" s="17">
-        <f>IF($H35="","",IFERROR(VLOOKUP($H35,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H35="","",IFERROR(VLOOKUP($H35,PQ_Diario!$A:$D,2,0),V35))</f>
         <v/>
       </c>
       <c r="J35" s="17">
-        <f>IF($H35="","",IFERROR(VLOOKUP($H35,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H35="","",IFERROR(VLOOKUP($H35,PQ_Diario!$A:$D,3,0),W35))</f>
         <v/>
       </c>
       <c r="K35" s="17">
-        <f>IF($H35="","",IFERROR(VLOOKUP($H35,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H35="","",IFERROR(VLOOKUP($H35,PQ_Diario!$A:$D,4,0),X35))</f>
         <v/>
       </c>
       <c r="S35" s="19" t="n">
@@ -2821,6 +2821,15 @@
       </c>
       <c r="U35" s="19" t="n">
         <v>0.07488</v>
+      </c>
+      <c r="V35" s="20" t="n">
+        <v>171.39</v>
+      </c>
+      <c r="W35" s="20" t="n">
+        <v>244.69</v>
+      </c>
+      <c r="X35" s="20" t="n">
+        <v>324.72</v>
       </c>
     </row>
     <row r="36">
@@ -6155,7 +6164,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6210,7 +6219,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>192.7</v>
+        <v>197</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>1</v>
@@ -6241,7 +6250,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>193.25</v>
+        <v>198.38</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>1</v>
@@ -6272,7 +6281,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>197.53</v>
+        <v>206.35</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6303,7 +6312,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>188.68</v>
+        <v>190.3</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6334,7 +6343,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>118.42</v>
+        <v>115.97</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6365,7 +6374,7 @@
         <v/>
       </c>
       <c r="D11" s="35" t="n">
-        <v>86.98999999999999</v>
+        <v>86.53</v>
       </c>
       <c r="E11" s="36" t="n">
         <v>0</v>
@@ -6391,7 +6400,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>167.55</v>
+        <v>170.25</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6417,7 +6426,7 @@
         <v/>
       </c>
       <c r="D13" s="35" t="n">
-        <v>94</v>
+        <v>93.5</v>
       </c>
       <c r="E13" s="36" t="n">
         <v>3</v>
@@ -6443,7 +6452,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>128.91</v>
+        <v>131.86</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6469,7 +6478,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>128</v>
+        <v>128.86</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>1</v>
@@ -6495,7 +6504,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>85.40000000000001</v>
+        <v>88.06</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6521,7 +6530,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>58.88</v>
+        <v>60.72</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6547,7 +6556,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>73</v>
+        <v>75.28</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6573,7 +6582,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>129.5</v>
+        <v>131</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6599,7 +6608,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>73.8</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6625,7 +6634,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>67.34999999999999</v>
+        <v>68</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>

--- a/excel/ACZO_Radar_Mercados.xlsx
+++ b/excel/ACZO_Radar_Mercados.xlsx
@@ -2861,15 +2861,15 @@
         <v/>
       </c>
       <c r="I36" s="17">
-        <f>IF($H36="","",IFERROR(VLOOKUP($H36,PQ_Diario!$A:$D,2,0),""))</f>
+        <f>IF($H36="","",IFERROR(VLOOKUP($H36,PQ_Diario!$A:$D,2,0),V36))</f>
         <v/>
       </c>
       <c r="J36" s="17">
-        <f>IF($H36="","",IFERROR(VLOOKUP($H36,PQ_Diario!$A:$D,3,0),""))</f>
+        <f>IF($H36="","",IFERROR(VLOOKUP($H36,PQ_Diario!$A:$D,3,0),W36))</f>
         <v/>
       </c>
       <c r="K36" s="17">
-        <f>IF($H36="","",IFERROR(VLOOKUP($H36,PQ_Diario!$A:$D,4,0),""))</f>
+        <f>IF($H36="","",IFERROR(VLOOKUP($H36,PQ_Diario!$A:$D,4,0),X36))</f>
         <v/>
       </c>
       <c r="S36" s="19" t="n">
@@ -2880,6 +2880,15 @@
       </c>
       <c r="U36" s="19" t="n">
         <v>0.07197000000000001</v>
+      </c>
+      <c r="V36" s="20" t="n">
+        <v>57.62</v>
+      </c>
+      <c r="W36" s="20" t="n">
+        <v>208.98</v>
+      </c>
+      <c r="X36" s="20" t="n">
+        <v>303.15</v>
       </c>
     </row>
     <row r="37">
@@ -3428,15 +3437,15 @@
         <v>46296</v>
       </c>
       <c r="B51" s="14">
-        <f>IFERROR(VLOOKUP($A51,PQ_Mensual!$A:$D,2,0),"")</f>
+        <f>IFERROR(VLOOKUP($A51,PQ_Mensual!$A:$D,2,0),S51)</f>
         <v/>
       </c>
       <c r="C51" s="14">
-        <f>IFERROR(VLOOKUP($A51,PQ_Mensual!$A:$D,3,0),"")</f>
+        <f>IFERROR(VLOOKUP($A51,PQ_Mensual!$A:$D,3,0),T51)</f>
         <v/>
       </c>
       <c r="D51" s="14">
-        <f>IFERROR(VLOOKUP($A51,PQ_Mensual!$A:$D,4,0),"")</f>
+        <f>IFERROR(VLOOKUP($A51,PQ_Mensual!$A:$D,4,0),U51)</f>
         <v/>
       </c>
       <c r="E51" s="14">
@@ -3446,6 +3455,15 @@
       <c r="F51" s="15">
         <f>IF(E51="","",E51*1000)</f>
         <v/>
+      </c>
+      <c r="S51" s="19" t="n">
+        <v>0.17314</v>
+      </c>
+      <c r="T51" s="19" t="n">
+        <v>0.1627</v>
+      </c>
+      <c r="U51" s="19" t="n">
+        <v>0.16533</v>
       </c>
     </row>
     <row r="52">
@@ -5668,15 +5686,15 @@
       <c r="C51" s="28" t="n"/>
       <c r="D51" s="28" t="n"/>
       <c r="E51" s="14">
-        <f>IFERROR(VLOOKUP($A51,PQ_Mensual6P!$A:$G,5,0),"")</f>
+        <f>IFERROR(VLOOKUP($A51,PQ_Mensual6P!$A:$G,5,0),V51)</f>
         <v/>
       </c>
       <c r="F51" s="14">
-        <f>IFERROR(VLOOKUP($A51,PQ_Mensual6P!$A:$G,6,0),"")</f>
+        <f>IFERROR(VLOOKUP($A51,PQ_Mensual6P!$A:$G,6,0),W51)</f>
         <v/>
       </c>
       <c r="G51" s="14">
-        <f>IFERROR(VLOOKUP($A51,PQ_Mensual6P!$A:$G,7,0),"")</f>
+        <f>IFERROR(VLOOKUP($A51,PQ_Mensual6P!$A:$G,7,0),X51)</f>
         <v/>
       </c>
       <c r="H51" s="15">
@@ -5687,6 +5705,15 @@
         <is>
           <t>BAJA</t>
         </is>
+      </c>
+      <c r="V51" s="19" t="n">
+        <v>0.17662</v>
+      </c>
+      <c r="W51" s="19" t="n">
+        <v>0.15674</v>
+      </c>
+      <c r="X51" s="19" t="n">
+        <v>0.16533</v>
       </c>
     </row>
     <row r="52">
@@ -6164,7 +6191,7 @@
         </is>
       </c>
       <c r="C4" s="31" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -6219,7 +6246,7 @@
         <v/>
       </c>
       <c r="D6" s="35" t="n">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E6" s="36" t="n">
         <v>1</v>
@@ -6250,7 +6277,7 @@
         <v/>
       </c>
       <c r="D7" s="35" t="n">
-        <v>198.38</v>
+        <v>192.5</v>
       </c>
       <c r="E7" s="36" t="n">
         <v>1</v>
@@ -6281,7 +6308,7 @@
         <v/>
       </c>
       <c r="D8" s="35" t="n">
-        <v>206.35</v>
+        <v>199.5</v>
       </c>
       <c r="E8" s="36" t="n">
         <v>0</v>
@@ -6312,7 +6339,7 @@
         <v/>
       </c>
       <c r="D9" s="35" t="n">
-        <v>190.3</v>
+        <v>192.91</v>
       </c>
       <c r="E9" s="36" t="n">
         <v>0</v>
@@ -6343,7 +6370,7 @@
         <v/>
       </c>
       <c r="D10" s="35" t="n">
-        <v>115.97</v>
+        <v>117.56</v>
       </c>
       <c r="E10" s="36" t="n">
         <v>0</v>
@@ -6400,7 +6427,7 @@
         <v/>
       </c>
       <c r="D12" s="35" t="n">
-        <v>170.25</v>
+        <v>169.25</v>
       </c>
       <c r="E12" s="36" t="n">
         <v>3</v>
@@ -6452,7 +6479,7 @@
         <v/>
       </c>
       <c r="D14" s="35" t="n">
-        <v>131.86</v>
+        <v>130.31</v>
       </c>
       <c r="E14" s="36" t="n">
         <v>3</v>
@@ -6478,7 +6505,7 @@
         <v/>
       </c>
       <c r="D15" s="35" t="n">
-        <v>128.86</v>
+        <v>129</v>
       </c>
       <c r="E15" s="36" t="n">
         <v>1</v>
@@ -6504,7 +6531,7 @@
         <v/>
       </c>
       <c r="D16" s="35" t="n">
-        <v>88.06</v>
+        <v>88.12</v>
       </c>
       <c r="E16" s="36" t="n">
         <v>0</v>
@@ -6530,7 +6557,7 @@
         <v/>
       </c>
       <c r="D17" s="35" t="n">
-        <v>60.72</v>
+        <v>60.76</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0</v>
@@ -6556,7 +6583,7 @@
         <v/>
       </c>
       <c r="D18" s="35" t="n">
-        <v>75.28</v>
+        <v>75.33</v>
       </c>
       <c r="E18" s="36" t="n">
         <v>0</v>
@@ -6582,7 +6609,7 @@
         <v/>
       </c>
       <c r="D19" s="35" t="n">
-        <v>131</v>
+        <v>130.4</v>
       </c>
       <c r="E19" s="36" t="n">
         <v>0</v>
@@ -6608,7 +6635,7 @@
         <v/>
       </c>
       <c r="D20" s="35" t="n">
-        <v>76.09999999999999</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>0</v>
@@ -6634,7 +6661,7 @@
         <v/>
       </c>
       <c r="D21" s="35" t="n">
-        <v>68</v>
+        <v>68.5</v>
       </c>
       <c r="E21" s="36" t="n">
         <v>0</v>
